--- a/observations/orbit_plans/mtp107/nomad_mtp107_plan.xlsx
+++ b/observations/orbit_plans/mtp107/nomad_mtp107_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="577">
   <si>
     <t>#orbitType</t>
   </si>
@@ -61,1504 +61,1510 @@
     <t xml:space="preserve">&amp;LST=12.1hrs; &amp;Angle=1; </t>
   </si>
   <si>
+    <t>6SUBD Nominal #54</t>
+  </si>
+  <si>
+    <t>2026 JUN 06 17:15:00</t>
+  </si>
+  <si>
+    <t>2026 JUN 06 19:12:58</t>
+  </si>
+  <si>
+    <t>6SUBD CO2 H2O #14</t>
+  </si>
+  <si>
+    <t>2026 JUN 06 21:10:53</t>
+  </si>
+  <si>
+    <t>2026 JUN 06 23:08:46</t>
+  </si>
+  <si>
+    <t>Dust H2O 01</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 01:06:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=12.0hrs; &amp;Angle=0; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #52</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 03:04:35</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 05:02:32</t>
+  </si>
+  <si>
+    <t>CO H2O 3SUBD #4</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 07:00:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:INSIGHT; &amp;daysideMatch:CURIOSITY; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 #24</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 08:58:27</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 10:56:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:NILI FOSSAE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 07 12:54:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.9hrs; &amp;Angle=0; </t>
+  </si>
+  <si>
+    <t>uvisNightLimb</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 14:52:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;trueNightLimb; </t>
+  </si>
+  <si>
+    <t>2026 JUN 07 16:50:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.9hrs; &amp;Angle=1; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 18:48:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>2026 JUN 07 20:46:00</t>
+  </si>
+  <si>
+    <t>2026 JUN 07 22:43:54</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #56</t>
+  </si>
+  <si>
+    <t>H2O 2SUBD 01</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 00:41:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ARSIA MONS; &amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 CO #27</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 02:39:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.8hrs; &amp;Angle=2; </t>
+  </si>
+  <si>
+    <t>2026 JUN 08 04:37:38</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #42</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 06:35:37</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 08:33:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.8hrs; &amp;Angle=3; </t>
+  </si>
+  <si>
+    <t>All Fullscan Fast #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 10:31:29</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 12:29:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.7hrs; &amp;Angle=3; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #48</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 14:27:15</t>
+  </si>
+  <si>
+    <t>6SUBD CH4 H2O #1</t>
+  </si>
+  <si>
+    <t>Surface Ice 6SUBD 01 136</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 16:25:11</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 18:23:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.7hrs; &amp;Angle=4; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 20:21:06</t>
+  </si>
+  <si>
+    <t>2026 JUN 08 22:19:01</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #45</t>
+  </si>
+  <si>
+    <t>CO 3SUBD #3</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 00:16:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;egressMatch:PHOENIX; &amp;daysideMatch:OLYMPICA FOSSAE-JOVIS THOLUS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 09 02:14:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.6hrs; &amp;Angle=5; </t>
+  </si>
+  <si>
+    <t>2026 JUN 09 04:12:44</t>
+  </si>
+  <si>
+    <t>6SUBD CO2 CO #29</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 06:10:42</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 08:08:40</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 10:06:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.6hrs; &amp;Angle=6; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #55</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 12:04:30</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 14:02:22</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 16:00:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.5hrs; &amp;Angle=6; </t>
+  </si>
+  <si>
+    <t>2026 JUN 09 17:58:15</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #57</t>
+  </si>
+  <si>
+    <t>H2O CO 3SUBD #3 136</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 19:56:13</t>
+  </si>
+  <si>
+    <t>2026 JUN 09 21:54:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.5hrs; &amp;Angle=7; </t>
+  </si>
+  <si>
+    <t>2026 JUN 09 23:52:04</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #51</t>
+  </si>
+  <si>
+    <t>2026 JUN 10 01:49:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=7; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 03:47:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=8; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 05:45:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;nomadDeimos; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 07:43:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:AEOLIS MENSAE MFF; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 09:41:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:TIANWEN1; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 11:39:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=9; </t>
+  </si>
+  <si>
+    <t>Fullscan fast step5 all #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 10 13:37:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.3hrs; &amp;Angle=9; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 15:35:26</t>
+  </si>
+  <si>
+    <t>2026 JUN 10 17:33:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;trueNightLimb; &amp;daysideMatch:MERIDIANI SULPHATES; </t>
+  </si>
+  <si>
+    <t>2026 JUN 10 19:31:21</t>
+  </si>
+  <si>
+    <t>2026 JUN 10 21:29:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.3hrs; &amp;Angle=10; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 H2O #12</t>
+  </si>
+  <si>
+    <t>CO H2O 3SUBD #3</t>
+  </si>
+  <si>
+    <t>2026 JUN 10 23:27:13</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 01:25:06</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #12</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 03:23:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=10; </t>
+  </si>
+  <si>
+    <t>2026 JUN 11 05:20:57</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 07:18:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=11; </t>
+  </si>
+  <si>
+    <t>2026 JUN 11 09:16:54</t>
+  </si>
+  <si>
+    <t>CO2 Fullscan Fast #3</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 11:14:50</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 13:12:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=12; </t>
+  </si>
+  <si>
+    <t>2026 JUN 11 15:10:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.1hrs; &amp;Angle=12; </t>
+  </si>
+  <si>
+    <t>CO2 Fullscan Fast #2</t>
+  </si>
+  <si>
+    <t>H2O CO 2SUBD #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 17:08:32</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 19:06:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ACIDALIA MUD VOLCANOES BASIN; </t>
+  </si>
+  <si>
+    <t>2026 JUN 11 21:04:28</t>
+  </si>
+  <si>
+    <t>2026 JUN 11 23:02:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.1hrs; &amp;Angle=13; </t>
+  </si>
+  <si>
+    <t>2026 JUN 12 01:00:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:SOUTH THAUMASIA; &amp;daysideMatch:ASCRAEUS MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 12 02:58:12</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 04:56:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.0hrs; &amp;Angle=13; </t>
+  </si>
+  <si>
+    <t>2026 JUN 12 06:54:06</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 08:52:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=11.0hrs; &amp;Angle=14; </t>
+  </si>
+  <si>
+    <t>2026 JUN 12 10:50:02</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 12:47:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 14:45:48</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 16:43:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.9hrs; &amp;Angle=15; </t>
+  </si>
+  <si>
+    <t>CO 3SUBD #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 18:41:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:VERNAL CRATER; </t>
+  </si>
+  <si>
+    <t>2026 JUN 12 20:39:40</t>
+  </si>
+  <si>
+    <t>2026 JUN 12 22:37:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:EASTERN COPRATES; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 H2O #11</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 00:35:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.9hrs; &amp;Angle=16; </t>
+  </si>
+  <si>
+    <t>2026 JUN 13 02:33:26</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 04:31:20</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 06:29:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.8hrs; &amp;Angle=16; </t>
+  </si>
+  <si>
+    <t>2026 JUN 13 08:27:17</t>
+  </si>
+  <si>
+    <t>6SUBD CO2 CO #25</t>
+  </si>
+  <si>
+    <t>H2O 3SUBD #1 136</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 10:25:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.8hrs; &amp;Angle=17; </t>
+  </si>
+  <si>
+    <t>2026 JUN 13 12:23:11</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 14:21:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;possibleOCM; </t>
+  </si>
+  <si>
+    <t>2026 JUN 13 16:18:58</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 18:16:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.7hrs; &amp;Angle=18; </t>
+  </si>
+  <si>
+    <t>LNO Occultation Fullscan Fast #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 20:14:53</t>
+  </si>
+  <si>
+    <t>2026 JUN 13 22:12:51</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 00:10:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;nomadDeimos; &amp;daysideMatch:EAST THAUMASIA; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 02:08:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:CLARITAS RISE; &amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 04:06:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.7hrs; &amp;Angle=19; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 06:04:32</t>
+  </si>
+  <si>
+    <t>CO 2SUBD 02</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 08:02:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.6hrs; &amp;Angle=19; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 10:00:29</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 11:58:27</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 13:56:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:PERSEVERANCE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 15:54:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.6hrs; &amp;Angle=20; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 17:52:10</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 19:50:08</t>
+  </si>
+  <si>
+    <t>uvisOnlyNightside</t>
+  </si>
+  <si>
+    <t>2026 JUN 14 21:48:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.5hrs; &amp;Angle=21; </t>
+  </si>
+  <si>
+    <t>2026 JUN 14 23:46:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:COPRATES RISE; </t>
+  </si>
+  <si>
+    <t>6SUBD Nom CO2 #1</t>
+  </si>
+  <si>
     <t>6SUBD DetLim #1</t>
   </si>
   <si>
-    <t>2026 JUN 06 17:15:00</t>
-  </si>
-  <si>
-    <t>2026 JUN 06 19:12:58</t>
-  </si>
-  <si>
-    <t>6SUBD CO2 H2O #11</t>
-  </si>
-  <si>
-    <t>2026 JUN 06 21:10:53</t>
-  </si>
-  <si>
-    <t>2026 JUN 06 23:08:46</t>
+    <t>2026 JUN 15 01:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:CERAUNIUS THOLUS; </t>
+  </si>
+  <si>
+    <t>CO 3SUBD #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 03:41:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ULYSSES THOLUS; </t>
+  </si>
+  <si>
+    <t>CO2 Fullscan Fast #4</t>
+  </si>
+  <si>
+    <t>6SUBD CO #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 05:39:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.5hrs; &amp;Angle=22; </t>
+  </si>
+  <si>
+    <t>2026 JUN 15 07:37:47</t>
+  </si>
+  <si>
+    <t>CO2 Fullscan Fast #5</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 09:35:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ELYSIUM MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 15 11:33:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.4hrs; &amp;Angle=22; </t>
   </si>
   <si>
     <t>Fullscan fast step4 all #1</t>
   </si>
   <si>
-    <t>2026 JUN 07 01:06:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=12.0hrs; &amp;Angle=0; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #56</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 03:04:35</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 05:02:32</t>
-  </si>
-  <si>
-    <t>Surface Ice 6SUBD 01 136</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 07:00:31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:INSIGHT; &amp;daysideMatch:CURIOSITY; </t>
+    <t>2026 JUN 15 13:31:41</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 15:29:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;nomadPhobos; </t>
+  </si>
+  <si>
+    <t>2026 JUN 15 17:27:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.4hrs; &amp;Angle=23; </t>
+  </si>
+  <si>
+    <t>6SUBD HCL H20 #1</t>
+  </si>
+  <si>
+    <t>6SUBD CO2 #19</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 19:25:26</t>
+  </si>
+  <si>
+    <t>H2O CO 2SUBD #3</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 21:23:25</t>
+  </si>
+  <si>
+    <t>2026 JUN 15 23:21:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.3hrs; &amp;Angle=24; </t>
+  </si>
+  <si>
+    <t>2026 JUN 16 01:19:19</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 03:17:13</t>
+  </si>
+  <si>
+    <t>HCL #10</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 05:15:07</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 07:13:04</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 09:11:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.3hrs; &amp;Angle=25; </t>
+  </si>
+  <si>
+    <t>2026 JUN 16 11:09:03</t>
+  </si>
+  <si>
+    <t>uvisOnlyLimb</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 13:07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;trueDayLimb; </t>
+  </si>
+  <si>
+    <t>2026 JUN 16 15:04:54</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 17:02:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.2hrs; &amp;Angle=25; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 #23</t>
+  </si>
+  <si>
+    <t>179 only #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 16 19:00:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.2hrs; &amp;Angle=26; </t>
+  </si>
+  <si>
+    <t>2026 JUN 16 20:58:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ACIDALIA MUD VOLCANOES NE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 16 22:56:42</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 00:54:40</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 02:52:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.1hrs; &amp;Angle=27; </t>
+  </si>
+  <si>
+    <t>2026 JUN 17 04:50:29</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 06:48:25</t>
+  </si>
+  <si>
+    <t>6SUBD Nom CO #7</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 08:46:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ELYSIUM CERBERUS PHLEGRA; </t>
+  </si>
+  <si>
+    <t>2026 JUN 17 10:44:23</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 12:42:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.1hrs; &amp;Angle=28; </t>
+  </si>
+  <si>
+    <t>2026 JUN 17 14:40:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.0hrs; &amp;Angle=28; </t>
+  </si>
+  <si>
+    <t>2026 JUN 17 16:38:11</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 18:36:06</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 20:34:04</t>
+  </si>
+  <si>
+    <t>168 only #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 17 22:32:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=10.0hrs; &amp;Angle=29; </t>
+  </si>
+  <si>
+    <t>CO Fullscan Fast #2</t>
+  </si>
+  <si>
+    <t>H2O CO 3SUBD #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 00:30:02</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 02:27:58</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 04:25:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:OLYMPICA FOSSAE-JOVIS THOLUS; &amp;daysideMatch:PAVONIS MONS; </t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #53</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 06:23:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;egressMatch:PHOENIX; </t>
+  </si>
+  <si>
+    <t>2026 JUN 18 08:21:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.9hrs; &amp;Angle=30; </t>
+  </si>
+  <si>
+    <t>2026 JUN 18 10:19:44</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 12:17:44</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 14:15:41</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 16:13:35</t>
+  </si>
+  <si>
+    <t>6SUBD CO2 H2O #13</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 18:11:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.9hrs; &amp;Angle=31; </t>
+  </si>
+  <si>
+    <t>2026 JUN 18 20:09:27</t>
+  </si>
+  <si>
+    <t>2026 JUN 18 22:07:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:MAWRTH VALLIS; &amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 00:05:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.8hrs; &amp;Angle=31; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 02:03:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.8hrs; &amp;Angle=32; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 04:01:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:CERAUNIUS FOSSAE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 05:59:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:OLYMPUS MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 07:57:10</t>
+  </si>
+  <si>
+    <t>2026 JUN 19 09:55:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=32; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 11:53:09</t>
+  </si>
+  <si>
+    <t>6SUBD Nominal #11</t>
+  </si>
+  <si>
+    <t>2026 JUN 19 13:51:08</t>
+  </si>
+  <si>
+    <t>2026 JUN 19 15:49:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=33; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 17:46:57</t>
+  </si>
+  <si>
+    <t>2026 JUN 19 19:44:53</t>
+  </si>
+  <si>
+    <t>2026 JUN 19 21:42:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:MERIDIANI SULPHATES; </t>
+  </si>
+  <si>
+    <t>2026 JUN 19 23:40:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=34; </t>
+  </si>
+  <si>
+    <t>2026 JUN 20 01:38:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.6hrs; &amp;Angle=34; </t>
+  </si>
+  <si>
+    <t>6SUBD CO #6</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 03:36:47</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 05:34:42</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 07:32:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.6hrs; &amp;Angle=35; </t>
+  </si>
+  <si>
+    <t>2026 JUN 20 09:30:36</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 11:28:37</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 13:26:37</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 15:24:34</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 17:22:28</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 19:20:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=36; </t>
+  </si>
+  <si>
+    <t>2026 JUN 20 21:18:22</t>
+  </si>
+  <si>
+    <t>2026 JUN 20 23:16:22</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 01:14:22</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 03:12:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=37; </t>
+  </si>
+  <si>
+    <t>2026 JUN 21 05:10:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ASCRAEUS MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 21 07:08:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.4hrs; &amp;Angle=37; </t>
+  </si>
+  <si>
+    <t>6SUBD CO2 CO #28</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 09:06:08</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 11:04:08</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 13:02:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.4hrs; &amp;Angle=38; </t>
+  </si>
+  <si>
+    <t>2026 JUN 21 15:00:08</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 16:58:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 18:55:58</t>
+  </si>
+  <si>
+    <t>6SUBD Nom CH4 #2</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 20:53:55</t>
+  </si>
+  <si>
+    <t>2026 JUN 21 22:51:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 00:49:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=39; </t>
+  </si>
+  <si>
+    <t>2026 JUN 22 02:47:55</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 04:45:52</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 06:43:47</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 08:41:44</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 10:39:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=40; </t>
+  </si>
+  <si>
+    <t>2026 JUN 22 12:37:45</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 14:35:46</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 16:33:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:UTOPIA; </t>
+  </si>
+  <si>
+    <t>2026 JUN 22 18:31:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=41; </t>
+  </si>
+  <si>
+    <t>2026 JUN 22 20:29:34</t>
+  </si>
+  <si>
+    <t>2026 JUN 22 22:27:34</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 00:25:35</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 02:23:35</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 04:21:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:EAST THAUMASIA; </t>
+  </si>
+  <si>
+    <t>Nominal 6SUBD #2</t>
+  </si>
+  <si>
+    <t>uvisLimb</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 06:19:28</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 08:17:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=42; </t>
+  </si>
+  <si>
+    <t>2026 JUN 23 10:15:24</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 12:13:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=42; </t>
+  </si>
+  <si>
+    <t>2026 JUN 23 14:11:26</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 16:09:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=43; </t>
+  </si>
+  <si>
+    <t>H2O CO 2SUBD #1</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 18:07:22</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 20:05:17</t>
+  </si>
+  <si>
+    <t>2026 JUN 23 22:03:16</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 00:01:17</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 01:59:19</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 03:57:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=44; </t>
+  </si>
+  <si>
+    <t>2026 JUN 24 05:55:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=44; </t>
+  </si>
+  <si>
+    <t>2026 JUN 24 07:53:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ARSIA MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 24 09:51:10</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 11:49:11</t>
   </si>
   <si>
     <t>6SUBD CO2 Dipole #1</t>
   </si>
   <si>
-    <t>2026 JUN 07 08:58:27</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 10:56:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:NILI FOSSAE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 07 12:54:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.9hrs; &amp;Angle=0; </t>
-  </si>
-  <si>
-    <t>uvisNightLimb</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 14:52:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;trueNightLimb; </t>
-  </si>
-  <si>
-    <t>2026 JUN 07 16:50:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.9hrs; &amp;Angle=1; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 #23</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 18:48:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>2026 JUN 07 20:46:00</t>
-  </si>
-  <si>
-    <t>2026 JUN 07 22:43:54</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #57</t>
-  </si>
-  <si>
-    <t>CO 3SUBD #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 00:41:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ARSIA MONS; &amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #42</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 02:39:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.8hrs; &amp;Angle=2; </t>
-  </si>
-  <si>
-    <t>2026 JUN 08 04:37:38</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #48</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 06:35:37</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 08:33:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.8hrs; &amp;Angle=3; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #55</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 10:31:29</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 12:29:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.7hrs; &amp;Angle=3; </t>
-  </si>
-  <si>
-    <t>6SUBD CH4 H2O #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 14:27:15</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 16:25:11</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 18:23:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.7hrs; &amp;Angle=4; </t>
-  </si>
-  <si>
-    <t>2026 JUN 08 20:21:06</t>
-  </si>
-  <si>
-    <t>2026 JUN 08 22:19:01</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #45</t>
-  </si>
-  <si>
-    <t>CO H2O 3SUBD #4</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 00:16:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;egressMatch:PHOENIX; &amp;daysideMatch:OLYMPICA FOSSAE-JOVIS THOLUS; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #54</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 02:14:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.6hrs; &amp;Angle=5; </t>
-  </si>
-  <si>
-    <t>2026 JUN 09 04:12:44</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 06:10:42</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 08:08:40</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #52</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 10:06:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.6hrs; &amp;Angle=6; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 CO #29</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 12:04:30</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 14:02:22</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 16:00:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.5hrs; &amp;Angle=6; </t>
-  </si>
-  <si>
-    <t>2026 JUN 09 17:58:15</t>
-  </si>
-  <si>
-    <t>CO2 Fullscan Fast #5</t>
-  </si>
-  <si>
-    <t>H2O CO 2SUBD #3</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 19:56:13</t>
-  </si>
-  <si>
-    <t>2026 JUN 09 21:54:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.5hrs; &amp;Angle=7; </t>
-  </si>
-  <si>
-    <t>2026 JUN 09 23:52:04</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 01:49:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=7; </t>
-  </si>
-  <si>
-    <t>2026 JUN 10 03:47:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=8; </t>
-  </si>
-  <si>
-    <t>2026 JUN 10 05:45:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;nomadDeimos; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 07:43:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:AEOLIS MENSAE MFF; </t>
-  </si>
-  <si>
-    <t>CO Fullscan Fast #2</t>
+    <t>2026 JUN 24 13:47:12</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 15:45:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=45; </t>
+  </si>
+  <si>
+    <t>2026 JUN 24 17:43:11</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 19:41:06</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 21:39:04</t>
+  </si>
+  <si>
+    <t>2026 JUN 24 23:37:05</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 01:35:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=46; </t>
+  </si>
+  <si>
+    <t>2026 JUN 25 03:33:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=46; </t>
+  </si>
+  <si>
+    <t>2026 JUN 25 05:31:05</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 07:29:02</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 09:26:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 11:24:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 13:23:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=47; </t>
+  </si>
+  <si>
+    <t>2026 JUN 25 15:21:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 17:19:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 19:17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ingressMatch:ARSIA MONS VOLCANIC CONES NE; &amp;daysideMatch:NILI FOSSAE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 25 21:14:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 25 23:12:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 01:10:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 03:09:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=48; </t>
+  </si>
+  <si>
+    <t>2026 JUN 26 05:07:01</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 07:04:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=48; </t>
+  </si>
+  <si>
+    <t>2026 JUN 26 09:02:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 11:00:55</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 12:58:57</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 14:57:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=49; </t>
+  </si>
+  <si>
+    <t>2026 JUN 26 16:55:01</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 18:52:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 20:50:55</t>
+  </si>
+  <si>
+    <t>2026 JUN 26 22:48:54</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 00:46:56</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 02:44:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ingressMatch:AEOLIS MENSAE MFF; &amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 04:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=50; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 06:40:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 08:38:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:PAVONIS MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 10:36:55</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 12:34:57</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 14:33:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;possibleOCM; &amp;daysideMatch:CERBERUS FOSSAE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 16:31:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=51; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 18:29:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 27 20:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ingressMatch:PAVONIS MONS; </t>
+  </si>
+  <si>
+    <t>2026 JUN 27 22:24:57</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 00:22:59</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 02:21:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 04:19:06</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 06:17:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=52; </t>
+  </si>
+  <si>
+    <t>2026 JUN 28 08:15:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:SOUTH THAUMASIA; </t>
+  </si>
+  <si>
+    <t>2026 JUN 28 10:13:03</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 12:11:04</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 14:09:07</t>
   </si>
   <si>
     <t>Surface 3SUBD #3</t>
   </si>
   <si>
-    <t>2026 JUN 10 09:41:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:TIANWEN1; </t>
-  </si>
-  <si>
-    <t>2026 JUN 10 11:39:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.4hrs; &amp;Angle=9; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 H2O #14</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 13:37:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.3hrs; &amp;Angle=9; </t>
-  </si>
-  <si>
-    <t>2026 JUN 10 15:35:26</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 17:33:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;trueNightLimb; &amp;daysideMatch:MERIDIANI SULPHATES; </t>
-  </si>
-  <si>
-    <t>2026 JUN 10 19:31:21</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 21:29:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.3hrs; &amp;Angle=10; </t>
-  </si>
-  <si>
-    <t>CO 3SUBD #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 10 23:27:13</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 01:25:06</t>
-  </si>
-  <si>
-    <t>6SUBD CO #6</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 03:23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=10; </t>
-  </si>
-  <si>
-    <t>2026 JUN 11 05:20:57</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 07:18:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=11; </t>
-  </si>
-  <si>
-    <t>2026 JUN 11 09:16:54</t>
-  </si>
-  <si>
-    <t>CO2 Fullscan Fast #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 11:14:50</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 13:12:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.2hrs; &amp;Angle=12; </t>
-  </si>
-  <si>
-    <t>2026 JUN 11 15:10:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.1hrs; &amp;Angle=12; </t>
-  </si>
-  <si>
-    <t>6SUBD CO #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 17:08:32</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 19:06:31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ACIDALIA MUD VOLCANOES BASIN; </t>
-  </si>
-  <si>
-    <t>2026 JUN 11 21:04:28</t>
-  </si>
-  <si>
-    <t>2026 JUN 11 23:02:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.1hrs; &amp;Angle=13; </t>
-  </si>
-  <si>
-    <t>2026 JUN 12 01:00:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:SOUTH THAUMASIA; &amp;daysideMatch:ASCRAEUS MONS; </t>
-  </si>
-  <si>
-    <t>LNO Occultation Fullscan Fast #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 02:58:12</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 04:56:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.0hrs; &amp;Angle=13; </t>
-  </si>
-  <si>
-    <t>CO 3SUBD #3</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 06:54:06</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 08:52:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=11.0hrs; &amp;Angle=14; </t>
-  </si>
-  <si>
-    <t>2026 JUN 12 10:50:02</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 12:47:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 14:45:48</t>
-  </si>
-  <si>
-    <t>6SUBD CO2 #24</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 16:43:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.9hrs; &amp;Angle=15; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #51</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 18:41:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:VERNAL CRATER; </t>
-  </si>
-  <si>
-    <t>2026 JUN 12 20:39:40</t>
-  </si>
-  <si>
-    <t>2026 JUN 12 22:37:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:EASTERN COPRATES; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 00:35:32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.9hrs; &amp;Angle=16; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 02:33:26</t>
-  </si>
-  <si>
-    <t>Dust H2O 01</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 04:31:20</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 06:29:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.8hrs; &amp;Angle=16; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 08:27:17</t>
-  </si>
-  <si>
-    <t>6SUBD CO2 H2O #13</t>
-  </si>
-  <si>
-    <t>CO H2O 3SUBD #3</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 10:25:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.8hrs; &amp;Angle=17; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 12:23:11</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 14:21:04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;possibleOCM; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 16:18:58</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 18:16:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.7hrs; &amp;Angle=18; </t>
-  </si>
-  <si>
-    <t>2026 JUN 13 20:14:53</t>
-  </si>
-  <si>
-    <t>2026 JUN 13 22:12:51</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 00:10:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;nomadDeimos; &amp;daysideMatch:EAST THAUMASIA; </t>
-  </si>
-  <si>
-    <t>2026 JUN 14 02:08:42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:CLARITAS RISE; &amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>2026 JUN 14 04:06:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.7hrs; &amp;Angle=19; </t>
-  </si>
-  <si>
-    <t>6SUBD Nom CO #7</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 06:04:32</t>
-  </si>
-  <si>
-    <t>H2O CO 3SUBD #3 136</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 08:02:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.6hrs; &amp;Angle=19; </t>
-  </si>
-  <si>
-    <t>2026 JUN 14 10:00:29</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 11:58:27</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 13:56:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:PERSEVERANCE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 14 15:54:14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.6hrs; &amp;Angle=20; </t>
-  </si>
-  <si>
-    <t>All Fullscan Fast #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 17:52:10</t>
-  </si>
-  <si>
-    <t>Fullscan fast step5 all #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 19:50:08</t>
-  </si>
-  <si>
-    <t>uvisOnlyNightside</t>
-  </si>
-  <si>
-    <t>2026 JUN 14 21:48:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.5hrs; &amp;Angle=21; </t>
-  </si>
-  <si>
-    <t>2026 JUN 14 23:46:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:COPRATES RISE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 01:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:CERAUNIUS THOLUS; </t>
+    <t>2026 JUN 28 16:07:11</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 18:05:13</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 20:03:12</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 22:01:09</t>
+  </si>
+  <si>
+    <t>2026 JUN 28 23:59:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=53; </t>
+  </si>
+  <si>
+    <t>2026 JUN 29 01:57:13</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 03:55:17</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 05:53:19</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 07:51:19</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 09:49:17</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 11:47:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=53; </t>
+  </si>
+  <si>
+    <t>2026 JUN 29 13:45:20</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 15:43:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=54; </t>
+  </si>
+  <si>
+    <t>2026 JUN 29 17:41:28</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 19:39:29</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 21:37:27</t>
+  </si>
+  <si>
+    <t>2026 JUN 29 23:35:26</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 01:33:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=54; </t>
+  </si>
+  <si>
+    <t>2026 JUN 30 03:31:35</t>
+  </si>
+  <si>
+    <t>Nominal 3SUBD 01</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 05:29:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;daysideMatch:ARGYRE; &amp;mroOverlap; </t>
+  </si>
+  <si>
+    <t>2026 JUN 30 07:27:40</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 09:25:39</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 11:23:38</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 13:21:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=55; </t>
+  </si>
+  <si>
+    <t>2026 JUN 30 15:19:45</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 17:17:50</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 19:15:53</t>
+  </si>
+  <si>
+    <t>2026 JUN 30 21:13:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;ingressMatch:CERAUNIUS FOSSAE; </t>
+  </si>
+  <si>
+    <t>2026 JUN 30 23:11:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=55; </t>
+  </si>
+  <si>
+    <t>2026 JUL 01 01:09:52</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 03:07:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=55; </t>
+  </si>
+  <si>
+    <t>2026 JUL 01 05:06:03</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 07:04:06</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 09:02:07</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 11:00:07</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 12:58:08</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 14:56:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=56; </t>
+  </si>
+  <si>
+    <t>2026 JUL 01 16:54:18</t>
+  </si>
+  <si>
+    <t>2026 JUL 01 18:52:22</t>
   </si>
   <si>
     <t>CO 2SUBD #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 03:41:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ULYSSES THOLUS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 05:39:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.5hrs; &amp;Angle=22; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 07:37:47</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 09:35:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ELYSIUM MONS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 11:33:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.4hrs; &amp;Angle=22; </t>
-  </si>
-  <si>
-    <t>179 only #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 13:31:41</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 15:29:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;nomadPhobos; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 17:27:28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.4hrs; &amp;Angle=23; </t>
-  </si>
-  <si>
-    <t>2026 JUN 15 19:25:26</t>
-  </si>
-  <si>
-    <t>H2O 3SUBD #1 136</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 21:23:25</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 15 23:21:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.3hrs; &amp;Angle=24; </t>
-  </si>
-  <si>
-    <t>2026 JUN 16 01:19:19</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 03:17:13</t>
-  </si>
-  <si>
-    <t>6SUBD HCL H20 #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 05:15:07</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 07:13:04</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 09:11:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.3hrs; &amp;Angle=25; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 CO #25</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 11:09:03</t>
-  </si>
-  <si>
-    <t>uvisOnlyLimb</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 13:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;trueDayLimb; </t>
-  </si>
-  <si>
-    <t>2026 JUN 16 15:04:54</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 17:02:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.2hrs; &amp;Angle=25; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 CO #27</t>
-  </si>
-  <si>
-    <t>168 only #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 19:00:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.2hrs; &amp;Angle=26; </t>
-  </si>
-  <si>
-    <t>CO2 Fullscan Fast #3</t>
-  </si>
-  <si>
-    <t>2026 JUN 16 20:58:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ACIDALIA MUD VOLCANOES NE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 16 22:56:42</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 00:54:40</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 02:52:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.1hrs; &amp;Angle=27; </t>
-  </si>
-  <si>
-    <t>2026 JUN 17 04:50:29</t>
-  </si>
-  <si>
-    <t>6SUBD CO2 #19</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 06:48:25</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 08:46:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ELYSIUM CERBERUS PHLEGRA; </t>
-  </si>
-  <si>
-    <t>2026 JUN 17 10:44:23</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #12</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 12:42:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.1hrs; &amp;Angle=28; </t>
-  </si>
-  <si>
-    <t>2026 JUN 17 14:40:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.0hrs; &amp;Angle=28; </t>
-  </si>
-  <si>
-    <t>2026 JUN 17 16:38:11</t>
-  </si>
-  <si>
-    <t>HCL #10</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 18:36:06</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 20:34:04</t>
-  </si>
-  <si>
-    <t>2026 JUN 17 22:32:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=10.0hrs; &amp;Angle=29; </t>
-  </si>
-  <si>
-    <t>2026 JUN 18 00:30:02</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 02:27:58</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 04:25:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:OLYMPICA FOSSAE-JOVIS THOLUS; &amp;daysideMatch:PAVONIS MONS; </t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #53</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 06:23:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;egressMatch:PHOENIX; </t>
-  </si>
-  <si>
-    <t>2026 JUN 18 08:21:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.9hrs; &amp;Angle=30; </t>
-  </si>
-  <si>
-    <t>2026 JUN 18 10:19:44</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 12:17:44</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 14:15:41</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 16:13:35</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 18:11:29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.9hrs; &amp;Angle=31; </t>
-  </si>
-  <si>
-    <t>2026 JUN 18 20:09:27</t>
-  </si>
-  <si>
-    <t>2026 JUN 18 22:07:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:MAWRTH VALLIS; &amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 00:05:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.8hrs; &amp;Angle=31; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 02:03:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.8hrs; &amp;Angle=32; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 04:01:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:CERAUNIUS FOSSAE; </t>
-  </si>
-  <si>
-    <t>6SUBD Nom CH4 #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 05:59:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:OLYMPUS MONS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 07:57:10</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 09:55:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=32; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 11:53:09</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 13:51:08</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 15:49:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=33; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 17:46:57</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 19:44:53</t>
-  </si>
-  <si>
-    <t>2026 JUN 19 21:42:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:MERIDIANI SULPHATES; </t>
-  </si>
-  <si>
-    <t>2026 JUN 19 23:40:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.7hrs; &amp;Angle=34; </t>
-  </si>
-  <si>
-    <t>2026 JUN 20 01:38:51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.6hrs; &amp;Angle=34; </t>
-  </si>
-  <si>
-    <t>2026 JUN 20 03:36:47</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 05:34:42</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 07:32:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.6hrs; &amp;Angle=35; </t>
-  </si>
-  <si>
-    <t>2026 JUN 20 09:30:36</t>
-  </si>
-  <si>
-    <t>CO 2SUBD 02</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 11:28:37</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 13:26:37</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 15:24:34</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 17:22:28</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 19:20:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=36; </t>
-  </si>
-  <si>
-    <t>2026 JUN 20 21:18:22</t>
-  </si>
-  <si>
-    <t>2026 JUN 20 23:16:22</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 01:14:22</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 03:12:19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=37; </t>
-  </si>
-  <si>
-    <t>2026 JUN 21 05:10:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ASCRAEUS MONS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 21 07:08:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.4hrs; &amp;Angle=37; </t>
-  </si>
-  <si>
-    <t>2026 JUN 21 09:06:08</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 11:04:08</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 13:02:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.4hrs; &amp;Angle=38; </t>
-  </si>
-  <si>
-    <t>2026 JUN 21 15:00:08</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 16:58:03</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 18:55:58</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 20:53:55</t>
-  </si>
-  <si>
-    <t>2026 JUN 21 22:51:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 00:49:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=39; </t>
-  </si>
-  <si>
-    <t>2026 JUN 22 02:47:55</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 04:45:52</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 06:43:47</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 08:41:44</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 10:39:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=40; </t>
-  </si>
-  <si>
-    <t>2026 JUN 22 12:37:45</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 14:35:46</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 16:33:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:UTOPIA; </t>
-  </si>
-  <si>
-    <t>2026 JUN 22 18:31:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=41; </t>
-  </si>
-  <si>
-    <t>2026 JUN 22 20:29:34</t>
-  </si>
-  <si>
-    <t>2026 JUN 22 22:27:34</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 00:25:35</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 02:23:35</t>
-  </si>
-  <si>
-    <t>6SUBD Nom CO2 #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 04:21:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:EAST THAUMASIA; </t>
-  </si>
-  <si>
-    <t>2026 JUN 23 06:19:28</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 08:17:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=42; </t>
-  </si>
-  <si>
-    <t>2026 JUN 23 10:15:24</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 12:13:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=42; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 CO #28</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 14:11:26</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 16:09:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=43; </t>
-  </si>
-  <si>
-    <t>2026 JUN 23 18:07:22</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 20:05:17</t>
-  </si>
-  <si>
-    <t>2026 JUN 23 22:03:16</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 00:01:17</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 01:59:19</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 03:57:18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=44; </t>
-  </si>
-  <si>
-    <t>2026 JUN 24 05:55:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=44; </t>
-  </si>
-  <si>
-    <t>H2O 2SUBD 01</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 07:53:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ARSIA MONS; </t>
-  </si>
-  <si>
-    <t>6SUBD CO2 H2O #12</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 09:51:10</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 11:49:11</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 13:47:12</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 15:45:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=45; </t>
-  </si>
-  <si>
-    <t>2026 JUN 24 17:43:11</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 19:41:06</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 21:39:04</t>
-  </si>
-  <si>
-    <t>2026 JUN 24 23:37:05</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 01:35:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=46; </t>
-  </si>
-  <si>
-    <t>2026 JUN 25 03:33:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=46; </t>
-  </si>
-  <si>
-    <t>2026 JUN 25 05:31:05</t>
-  </si>
-  <si>
-    <t>Nominal 3SUBD 01</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 07:29:02</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 09:26:59</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 11:24:59</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 13:23:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=47; </t>
-  </si>
-  <si>
-    <t>2026 JUN 25 15:21:03</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 17:19:03</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 19:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;ingressMatch:ARSIA MONS VOLCANIC CONES NE; &amp;daysideMatch:NILI FOSSAE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 25 21:14:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 25 23:12:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 01:10:59</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 03:09:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=48; </t>
-  </si>
-  <si>
-    <t>2026 JUN 26 05:07:01</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 07:04:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=48; </t>
-  </si>
-  <si>
-    <t>2026 JUN 26 09:02:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 11:00:55</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 12:58:57</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 14:57:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=49; </t>
-  </si>
-  <si>
-    <t>2026 JUN 26 16:55:01</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 18:52:59</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 20:50:55</t>
-  </si>
-  <si>
-    <t>2026 JUN 26 22:48:54</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 00:46:56</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 02:44:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;ingressMatch:AEOLIS MENSAE MFF; &amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 04:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=50; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 06:40:59</t>
-  </si>
-  <si>
-    <t>CO2 Fullscan Fast #4</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 08:38:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:PAVONIS MONS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 10:36:55</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 12:34:57</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 14:33:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;possibleOCM; &amp;daysideMatch:CERBERUS FOSSAE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 16:31:03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=51; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 18:29:03</t>
-  </si>
-  <si>
-    <t>2026 JUN 27 20:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;ingressMatch:PAVONIS MONS; </t>
-  </si>
-  <si>
-    <t>2026 JUN 27 22:24:57</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 00:22:59</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 02:21:03</t>
-  </si>
-  <si>
-    <t>H2O CO 2SUBD #1</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 04:19:06</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 06:17:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=52; </t>
-  </si>
-  <si>
-    <t>2026 JUN 28 08:15:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:SOUTH THAUMASIA; </t>
-  </si>
-  <si>
-    <t>2026 JUN 28 10:13:03</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 12:11:04</t>
-  </si>
-  <si>
-    <t>6SUBD Nominal #11</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 14:09:07</t>
-  </si>
-  <si>
-    <t>H2O CO 2SUBD #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 16:07:11</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 18:05:13</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 20:03:12</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 22:01:09</t>
-  </si>
-  <si>
-    <t>2026 JUN 28 23:59:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.8hrs; &amp;Angle=53; </t>
-  </si>
-  <si>
-    <t>2026 JUN 29 01:57:13</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 03:55:17</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 05:53:19</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 07:51:19</t>
-  </si>
-  <si>
-    <t>H2O CO 3SUBD #2</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 09:49:17</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 11:47:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=53; </t>
-  </si>
-  <si>
-    <t>2026 JUN 29 13:45:20</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 15:43:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=8.9hrs; &amp;Angle=54; </t>
-  </si>
-  <si>
-    <t>2026 JUN 29 17:41:28</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 19:39:29</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 21:37:27</t>
-  </si>
-  <si>
-    <t>2026 JUN 29 23:35:26</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 01:33:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.0hrs; &amp;Angle=54; </t>
-  </si>
-  <si>
-    <t>2026 JUN 30 03:31:35</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 05:29:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;daysideMatch:ARGYRE; &amp;mroOverlap; </t>
-  </si>
-  <si>
-    <t>2026 JUN 30 07:27:40</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 09:25:39</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 11:23:38</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 13:21:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.1hrs; &amp;Angle=55; </t>
-  </si>
-  <si>
-    <t>2026 JUN 30 15:19:45</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 17:17:50</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 19:15:53</t>
-  </si>
-  <si>
-    <t>2026 JUN 30 21:13:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;ingressMatch:CERAUNIUS FOSSAE; </t>
-  </si>
-  <si>
-    <t>2026 JUN 30 23:11:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.2hrs; &amp;Angle=55; </t>
-  </si>
-  <si>
-    <t>2026 JUL 01 01:09:52</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 03:07:58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.3hrs; &amp;Angle=55; </t>
-  </si>
-  <si>
-    <t>2026 JUL 01 05:06:03</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 07:04:06</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 09:02:07</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 11:00:07</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 12:58:08</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 14:56:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;LST=9.5hrs; &amp;Angle=56; </t>
-  </si>
-  <si>
-    <t>2026 JUL 01 16:54:18</t>
-  </si>
-  <si>
-    <t>2026 JUL 01 18:52:22</t>
   </si>
   <si>
     <t>2026 JUL 01 20:50:24</t>
@@ -2574,22 +2580,22 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
         <v>6</v>
       </c>
       <c r="H27" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="I27" t="s">
         <v>8</v>
       </c>
       <c r="L27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M27" t="s">
         <v>61</v>
@@ -2603,10 +2609,10 @@
         <v>8</v>
       </c>
       <c r="L28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2614,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" t="s">
         <v>6</v>
@@ -2626,10 +2632,10 @@
         <v>8</v>
       </c>
       <c r="L29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2640,10 +2646,10 @@
         <v>8</v>
       </c>
       <c r="L30" t="s">
+        <v>71</v>
+      </c>
+      <c r="M30" t="s">
         <v>68</v>
-      </c>
-      <c r="M30" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2651,25 +2657,25 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
         <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
         <v>8</v>
       </c>
       <c r="L31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -2677,10 +2683,10 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -2689,10 +2695,10 @@
         <v>8</v>
       </c>
       <c r="L32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -2703,10 +2709,10 @@
         <v>8</v>
       </c>
       <c r="L33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2714,10 +2720,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>3</v>
@@ -2726,10 +2732,10 @@
         <v>8</v>
       </c>
       <c r="L34" t="s">
+        <v>80</v>
+      </c>
+      <c r="M34" t="s">
         <v>77</v>
-      </c>
-      <c r="M34" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2740,10 +2746,10 @@
         <v>8</v>
       </c>
       <c r="L35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2751,10 +2757,10 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -2763,10 +2769,10 @@
         <v>8</v>
       </c>
       <c r="L36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2774,10 +2780,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
         <v>6</v>
@@ -2786,10 +2792,10 @@
         <v>8</v>
       </c>
       <c r="L37" t="s">
+        <v>85</v>
+      </c>
+      <c r="M37" t="s">
         <v>83</v>
-      </c>
-      <c r="M37" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2800,7 +2806,7 @@
         <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
         <v>38</v>
@@ -2814,10 +2820,10 @@
         <v>8</v>
       </c>
       <c r="L39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M39" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2828,10 +2834,10 @@
         <v>8</v>
       </c>
       <c r="L40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2839,22 +2845,22 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
         <v>6</v>
       </c>
       <c r="H41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s">
         <v>8</v>
       </c>
       <c r="L41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M41" t="s">
         <v>43</v>
@@ -2868,10 +2874,10 @@
         <v>8</v>
       </c>
       <c r="L42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2882,10 +2888,10 @@
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2893,10 +2899,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="G44" t="s">
         <v>6</v>
@@ -2905,10 +2911,10 @@
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2916,10 +2922,10 @@
         <v>14</v>
       </c>
       <c r="L45" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M45" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2927,10 +2933,10 @@
         <v>14</v>
       </c>
       <c r="L46" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M46" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2938,10 +2944,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G47" t="s">
         <v>6</v>
@@ -2950,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2961,16 +2967,16 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
         <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
         <v>8</v>
@@ -3080,22 +3086,22 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
       </c>
       <c r="H55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I55" t="s">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M55" t="s">
         <v>117</v>
@@ -3109,7 +3115,7 @@
         <v>8</v>
       </c>
       <c r="L56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M56" t="s">
         <v>117</v>
@@ -3120,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
         <v>3</v>
@@ -3132,10 +3138,10 @@
         <v>8</v>
       </c>
       <c r="L57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3146,7 +3152,7 @@
         <v>36</v>
       </c>
       <c r="L58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M58" t="s">
         <v>38</v>
@@ -3157,10 +3163,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s">
         <v>6</v>
@@ -3169,10 +3175,10 @@
         <v>8</v>
       </c>
       <c r="L59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -3183,10 +3189,10 @@
         <v>8</v>
       </c>
       <c r="L60" t="s">
+        <v>128</v>
+      </c>
+      <c r="M60" t="s">
         <v>127</v>
-      </c>
-      <c r="M60" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -3194,10 +3200,10 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G61" t="s">
         <v>6</v>
@@ -3206,10 +3212,10 @@
         <v>8</v>
       </c>
       <c r="L61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -3220,10 +3226,10 @@
         <v>8</v>
       </c>
       <c r="L62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -3231,10 +3237,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F63" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G63" t="s">
         <v>6</v>
@@ -3243,10 +3249,10 @@
         <v>8</v>
       </c>
       <c r="L63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -3254,25 +3260,25 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" t="s">
+        <v>3</v>
+      </c>
+      <c r="H64" t="s">
+        <v>136</v>
+      </c>
+      <c r="I64" t="s">
+        <v>8</v>
+      </c>
+      <c r="L64" t="s">
+        <v>137</v>
+      </c>
+      <c r="M64" t="s">
         <v>134</v>
-      </c>
-      <c r="C64" t="s">
-        <v>134</v>
-      </c>
-      <c r="D64" t="s">
-        <v>3</v>
-      </c>
-      <c r="H64" t="s">
-        <v>118</v>
-      </c>
-      <c r="I64" t="s">
-        <v>8</v>
-      </c>
-      <c r="L64" t="s">
-        <v>135</v>
-      </c>
-      <c r="M64" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -3283,10 +3289,10 @@
         <v>8</v>
       </c>
       <c r="L65" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3297,10 +3303,10 @@
         <v>8</v>
       </c>
       <c r="L66" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -3308,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
         <v>3</v>
@@ -3320,10 +3326,10 @@
         <v>8</v>
       </c>
       <c r="L67" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -3334,10 +3340,10 @@
         <v>8</v>
       </c>
       <c r="L68" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M68" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -3345,10 +3351,10 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="D69" t="s">
         <v>3</v>
@@ -3357,10 +3363,10 @@
         <v>8</v>
       </c>
       <c r="L69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M69" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -3368,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F70" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G70" t="s">
         <v>6</v>
@@ -3380,10 +3386,10 @@
         <v>8</v>
       </c>
       <c r="L70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -3391,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="H71" t="s">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="I71" t="s">
         <v>8</v>
@@ -3408,10 +3414,10 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="F72" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="G72" t="s">
         <v>6</v>
@@ -3445,10 +3451,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="G74" t="s">
         <v>6</v>
@@ -3482,22 +3488,22 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
+        <v>64</v>
+      </c>
+      <c r="F76" t="s">
+        <v>64</v>
+      </c>
+      <c r="G76" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" t="s">
         <v>154</v>
       </c>
-      <c r="F76" t="s">
-        <v>154</v>
-      </c>
-      <c r="G76" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" t="s">
-        <v>8</v>
-      </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>155</v>
-      </c>
-      <c r="M76" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -3505,25 +3511,25 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77" t="s">
+        <v>156</v>
+      </c>
+      <c r="I77" t="s">
+        <v>8</v>
+      </c>
+      <c r="L77" t="s">
         <v>157</v>
       </c>
-      <c r="C77" t="s">
-        <v>157</v>
-      </c>
-      <c r="D77" t="s">
-        <v>3</v>
-      </c>
-      <c r="H77" t="s">
-        <v>147</v>
-      </c>
-      <c r="I77" t="s">
-        <v>8</v>
-      </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>158</v>
-      </c>
-      <c r="M77" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -3534,10 +3540,10 @@
         <v>8</v>
       </c>
       <c r="L78" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -3548,10 +3554,10 @@
         <v>8</v>
       </c>
       <c r="L79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M79" t="s">
         <v>161</v>
-      </c>
-      <c r="M79" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -3559,10 +3565,10 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D80" t="s">
         <v>3</v>
@@ -3596,19 +3602,19 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
+        <v>109</v>
+      </c>
+      <c r="C82" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" t="s">
+        <v>8</v>
+      </c>
+      <c r="L82" t="s">
         <v>166</v>
-      </c>
-      <c r="C82" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82" t="s">
-        <v>3</v>
-      </c>
-      <c r="I82" t="s">
-        <v>8</v>
-      </c>
-      <c r="L82" t="s">
-        <v>167</v>
       </c>
       <c r="M82" t="s">
         <v>164</v>
@@ -3622,10 +3628,10 @@
         <v>8</v>
       </c>
       <c r="L83" t="s">
+        <v>167</v>
+      </c>
+      <c r="M83" t="s">
         <v>168</v>
-      </c>
-      <c r="M83" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3633,10 +3639,10 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="D84" t="s">
         <v>3</v>
@@ -3645,10 +3651,10 @@
         <v>8</v>
       </c>
       <c r="L84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3656,25 +3662,25 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
+        <v>170</v>
+      </c>
+      <c r="F85" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" t="s">
+        <v>6</v>
+      </c>
+      <c r="H85" t="s">
         <v>171</v>
       </c>
-      <c r="F85" t="s">
-        <v>171</v>
-      </c>
-      <c r="G85" t="s">
-        <v>6</v>
-      </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
+        <v>8</v>
+      </c>
+      <c r="L85" t="s">
         <v>172</v>
       </c>
-      <c r="I85" t="s">
-        <v>8</v>
-      </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>173</v>
-      </c>
-      <c r="M85" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3682,10 +3688,10 @@
         <v>14</v>
       </c>
       <c r="L86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3693,10 +3699,10 @@
         <v>14</v>
       </c>
       <c r="L87" t="s">
+        <v>175</v>
+      </c>
+      <c r="M87" t="s">
         <v>176</v>
-      </c>
-      <c r="M87" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3707,10 +3713,10 @@
         <v>8</v>
       </c>
       <c r="L88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3721,10 +3727,10 @@
         <v>8</v>
       </c>
       <c r="L89" t="s">
+        <v>178</v>
+      </c>
+      <c r="M89" t="s">
         <v>179</v>
-      </c>
-      <c r="M89" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3732,16 +3738,16 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="F90" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="G90" t="s">
         <v>6</v>
       </c>
       <c r="H90" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="I90" t="s">
         <v>8</v>
@@ -3750,7 +3756,7 @@
         <v>181</v>
       </c>
       <c r="M90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3761,7 +3767,7 @@
         <v>182</v>
       </c>
       <c r="M91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3808,19 +3814,19 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
+        <v>90</v>
+      </c>
+      <c r="F95" t="s">
+        <v>90</v>
+      </c>
+      <c r="G95" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" t="s">
+        <v>8</v>
+      </c>
+      <c r="L95" t="s">
         <v>189</v>
-      </c>
-      <c r="F95" t="s">
-        <v>189</v>
-      </c>
-      <c r="G95" t="s">
-        <v>6</v>
-      </c>
-      <c r="I95" t="s">
-        <v>8</v>
-      </c>
-      <c r="L95" t="s">
-        <v>190</v>
       </c>
       <c r="M95" t="s">
         <v>188</v>
@@ -3831,25 +3837,25 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
         <v>3</v>
       </c>
       <c r="H96" t="s">
+        <v>190</v>
+      </c>
+      <c r="I96" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" t="s">
         <v>191</v>
       </c>
-      <c r="I96" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="M96" t="s">
         <v>192</v>
-      </c>
-      <c r="M96" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3860,7 +3866,7 @@
         <v>8</v>
       </c>
       <c r="L97" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M97" t="s">
         <v>29</v>
@@ -3874,7 +3880,7 @@
         <v>36</v>
       </c>
       <c r="L98" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M98" t="s">
         <v>38</v>
@@ -3885,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D99" t="s">
         <v>3</v>
@@ -3897,10 +3903,10 @@
         <v>8</v>
       </c>
       <c r="L99" t="s">
+        <v>195</v>
+      </c>
+      <c r="M99" t="s">
         <v>196</v>
-      </c>
-      <c r="M99" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3911,10 +3917,10 @@
         <v>8</v>
       </c>
       <c r="L100" t="s">
+        <v>197</v>
+      </c>
+      <c r="M100" t="s">
         <v>198</v>
-      </c>
-      <c r="M100" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3922,25 +3928,25 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="C101" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="D101" t="s">
         <v>3</v>
       </c>
       <c r="H101" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="I101" t="s">
         <v>8</v>
       </c>
       <c r="L101" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3948,10 +3954,10 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
         <v>6</v>
@@ -3960,10 +3966,10 @@
         <v>8</v>
       </c>
       <c r="L102" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M102" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3974,13 +3980,13 @@
         <v>8</v>
       </c>
       <c r="K103" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L103" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M103" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3991,10 +3997,10 @@
         <v>8</v>
       </c>
       <c r="L104" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M104" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -4002,19 +4008,19 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C105" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D105" t="s">
         <v>3</v>
       </c>
       <c r="E105" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="F105" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="G105" t="s">
         <v>6</v>
@@ -4023,10 +4029,10 @@
         <v>8</v>
       </c>
       <c r="L105" t="s">
+        <v>208</v>
+      </c>
+      <c r="M105" t="s">
         <v>209</v>
-      </c>
-      <c r="M105" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -4034,16 +4040,16 @@
         <v>3</v>
       </c>
       <c r="H106" t="s">
+        <v>210</v>
+      </c>
+      <c r="I106" t="s">
+        <v>8</v>
+      </c>
+      <c r="L106" t="s">
         <v>211</v>
       </c>
-      <c r="I106" t="s">
-        <v>8</v>
-      </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>212</v>
-      </c>
-      <c r="M106" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -4051,19 +4057,19 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="D107" t="s">
         <v>3</v>
       </c>
       <c r="E107" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="F107" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="G107" t="s">
         <v>6</v>
@@ -4072,10 +4078,10 @@
         <v>8</v>
       </c>
       <c r="L107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -4086,10 +4092,10 @@
         <v>8</v>
       </c>
       <c r="L108" t="s">
+        <v>217</v>
+      </c>
+      <c r="M108" t="s">
         <v>216</v>
-      </c>
-      <c r="M108" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -4097,19 +4103,19 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C109" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="D109" t="s">
         <v>3</v>
       </c>
       <c r="E109" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F109" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
         <v>6</v>
@@ -4118,10 +4124,10 @@
         <v>8</v>
       </c>
       <c r="L109" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M109" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -4132,10 +4138,10 @@
         <v>8</v>
       </c>
       <c r="L110" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M110" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -4143,19 +4149,19 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C111" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D111" t="s">
         <v>3</v>
       </c>
       <c r="L111" t="s">
+        <v>224</v>
+      </c>
+      <c r="M111" t="s">
         <v>222</v>
-      </c>
-      <c r="M111" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -4163,10 +4169,10 @@
         <v>14</v>
       </c>
       <c r="L112" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M112" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -4177,10 +4183,10 @@
         <v>8</v>
       </c>
       <c r="L113" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M113" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -4188,19 +4194,19 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="C114" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="D114" t="s">
         <v>3</v>
       </c>
       <c r="E114" t="s">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="F114" t="s">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="G114" t="s">
         <v>6</v>
@@ -4209,10 +4215,10 @@
         <v>8</v>
       </c>
       <c r="L114" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M114" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -4220,13 +4226,13 @@
         <v>3</v>
       </c>
       <c r="H115" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
       </c>
       <c r="L115" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M115" t="s">
         <v>43</v>
@@ -4237,10 +4243,10 @@
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="F116" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="G116" t="s">
         <v>6</v>
@@ -4249,10 +4255,10 @@
         <v>8</v>
       </c>
       <c r="L116" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M116" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -4263,10 +4269,10 @@
         <v>8</v>
       </c>
       <c r="L117" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M117" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -4277,10 +4283,10 @@
         <v>8</v>
       </c>
       <c r="L118" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M118" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -4288,31 +4294,31 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="D119" t="s">
         <v>3</v>
       </c>
       <c r="E119" t="s">
+        <v>64</v>
+      </c>
+      <c r="F119" t="s">
+        <v>64</v>
+      </c>
+      <c r="G119" t="s">
+        <v>6</v>
+      </c>
+      <c r="I119" t="s">
+        <v>8</v>
+      </c>
+      <c r="L119" t="s">
+        <v>239</v>
+      </c>
+      <c r="M119" t="s">
         <v>235</v>
-      </c>
-      <c r="F119" t="s">
-        <v>235</v>
-      </c>
-      <c r="G119" t="s">
-        <v>6</v>
-      </c>
-      <c r="I119" t="s">
-        <v>8</v>
-      </c>
-      <c r="L119" t="s">
-        <v>236</v>
-      </c>
-      <c r="M119" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -4320,31 +4326,31 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="C120" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="D120" t="s">
         <v>3</v>
       </c>
       <c r="E120" t="s">
+        <v>84</v>
+      </c>
+      <c r="F120" t="s">
+        <v>84</v>
+      </c>
+      <c r="G120" t="s">
+        <v>6</v>
+      </c>
+      <c r="I120" t="s">
+        <v>8</v>
+      </c>
+      <c r="L120" t="s">
+        <v>240</v>
+      </c>
+      <c r="M120" t="s">
         <v>235</v>
-      </c>
-      <c r="F120" t="s">
-        <v>235</v>
-      </c>
-      <c r="G120" t="s">
-        <v>6</v>
-      </c>
-      <c r="I120" t="s">
-        <v>8</v>
-      </c>
-      <c r="L120" t="s">
-        <v>237</v>
-      </c>
-      <c r="M120" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -4355,10 +4361,10 @@
         <v>8</v>
       </c>
       <c r="L121" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M121" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -4366,19 +4372,19 @@
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="C122" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="D122" t="s">
         <v>3</v>
       </c>
       <c r="E122" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F122" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="G122" t="s">
         <v>6</v>
@@ -4387,7 +4393,7 @@
         <v>8</v>
       </c>
       <c r="L122" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M122" t="s">
         <v>29</v>
@@ -4398,13 +4404,13 @@
         <v>28</v>
       </c>
       <c r="I123" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L123" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M123" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -4415,7 +4421,7 @@
         <v>8</v>
       </c>
       <c r="L124" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M124" t="s">
         <v>33</v>
@@ -4429,10 +4435,10 @@
         <v>8</v>
       </c>
       <c r="L125" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M125" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4440,19 +4446,19 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C126" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D126" t="s">
         <v>3</v>
       </c>
       <c r="E126" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F126" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G126" t="s">
         <v>6</v>
@@ -4461,10 +4467,10 @@
         <v>8</v>
       </c>
       <c r="L126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M126" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4472,19 +4478,19 @@
         <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>252</v>
+        <v>54</v>
       </c>
       <c r="C127" t="s">
-        <v>252</v>
+        <v>54</v>
       </c>
       <c r="D127" t="s">
         <v>3</v>
       </c>
       <c r="E127" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F127" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="G127" t="s">
         <v>6</v>
@@ -4493,10 +4499,10 @@
         <v>8</v>
       </c>
       <c r="L127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4507,13 +4513,13 @@
         <v>8</v>
       </c>
       <c r="K128" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M128" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4521,25 +4527,25 @@
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F129" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s">
         <v>6</v>
       </c>
       <c r="H129" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="I129" t="s">
         <v>8</v>
       </c>
       <c r="L129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M129" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4550,10 +4556,10 @@
         <v>8</v>
       </c>
       <c r="L130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M130" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4564,10 +4570,10 @@
         <v>8</v>
       </c>
       <c r="L131" t="s">
+        <v>260</v>
+      </c>
+      <c r="M131" t="s">
         <v>259</v>
-      </c>
-      <c r="M131" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4575,19 +4581,19 @@
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="C132" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="D132" t="s">
         <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F132" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G132" t="s">
         <v>6</v>
@@ -4599,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="M132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4607,19 +4613,19 @@
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="D133" t="s">
         <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="F133" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="G133" t="s">
         <v>6</v>
@@ -4628,10 +4634,10 @@
         <v>8</v>
       </c>
       <c r="L133" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4642,10 +4648,10 @@
         <v>8</v>
       </c>
       <c r="L134" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4653,19 +4659,19 @@
         <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="C135" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="D135" t="s">
         <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="F135" t="s">
-        <v>79</v>
+        <v>250</v>
       </c>
       <c r="G135" t="s">
         <v>6</v>
@@ -4713,28 +4719,28 @@
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C138" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D138" t="s">
         <v>3</v>
       </c>
       <c r="E138" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>6</v>
+      </c>
+      <c r="I138" t="s">
+        <v>8</v>
+      </c>
+      <c r="L138" t="s">
         <v>271</v>
-      </c>
-      <c r="F138" t="s">
-        <v>271</v>
-      </c>
-      <c r="G138" t="s">
-        <v>6</v>
-      </c>
-      <c r="I138" t="s">
-        <v>8</v>
-      </c>
-      <c r="L138" t="s">
-        <v>272</v>
       </c>
       <c r="M138" t="s">
         <v>269</v>
@@ -4748,7 +4754,7 @@
         <v>8</v>
       </c>
       <c r="L139" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M139" t="s">
         <v>269</v>
@@ -4759,19 +4765,19 @@
         <v>1</v>
       </c>
       <c r="B140" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C140" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D140" t="s">
         <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="F140" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="G140" t="s">
         <v>6</v>
@@ -4791,22 +4797,22 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
       <c r="F141" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
       <c r="G141" t="s">
         <v>6</v>
       </c>
       <c r="H141" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="I141" t="s">
         <v>8</v>
       </c>
       <c r="L141" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M141" t="s">
         <v>43</v>
@@ -4820,7 +4826,7 @@
         <v>8</v>
       </c>
       <c r="L142" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M142" t="s">
         <v>275</v>
@@ -4834,10 +4840,10 @@
         <v>8</v>
       </c>
       <c r="L143" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M143" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4845,19 +4851,19 @@
         <v>1</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C144" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D144" t="s">
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F144" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G144" t="s">
         <v>6</v>
@@ -4866,10 +4872,10 @@
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M144" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4880,10 +4886,10 @@
         <v>8</v>
       </c>
       <c r="L145" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M145" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4891,19 +4897,19 @@
         <v>1</v>
       </c>
       <c r="B146" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="C146" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="D146" t="s">
         <v>3</v>
       </c>
       <c r="E146" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="F146" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="G146" t="s">
         <v>6</v>
@@ -4912,10 +4918,10 @@
         <v>8</v>
       </c>
       <c r="L146" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M146" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4926,10 +4932,10 @@
         <v>8</v>
       </c>
       <c r="L147" t="s">
+        <v>288</v>
+      </c>
+      <c r="M147" t="s">
         <v>286</v>
-      </c>
-      <c r="M147" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4940,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="L148" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M148" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4951,19 +4957,19 @@
         <v>1</v>
       </c>
       <c r="B149" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="D149" t="s">
         <v>3</v>
       </c>
       <c r="E149" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="F149" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="G149" t="s">
         <v>6</v>
@@ -4972,7 +4978,7 @@
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M149" t="s">
         <v>43</v>
@@ -4983,28 +4989,28 @@
         <v>1</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="C150" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="D150" t="s">
         <v>3</v>
       </c>
       <c r="E150" t="s">
-        <v>62</v>
+        <v>291</v>
       </c>
       <c r="F150" t="s">
-        <v>62</v>
+        <v>291</v>
       </c>
       <c r="G150" t="s">
         <v>6</v>
       </c>
       <c r="L150" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M150" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -5012,10 +5018,10 @@
         <v>14</v>
       </c>
       <c r="L151" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M151" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -5026,10 +5032,10 @@
         <v>8</v>
       </c>
       <c r="L152" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M152" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -5037,10 +5043,10 @@
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="F153" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="G153" t="s">
         <v>6</v>
@@ -5049,10 +5055,10 @@
         <v>8</v>
       </c>
       <c r="L153" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M153" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -5063,10 +5069,10 @@
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M154" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -5074,19 +5080,19 @@
         <v>1</v>
       </c>
       <c r="B155" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="D155" t="s">
         <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="F155" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="G155" t="s">
         <v>6</v>
@@ -5095,10 +5101,10 @@
         <v>8</v>
       </c>
       <c r="L155" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M155" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -5106,25 +5112,25 @@
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="F156" t="s">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="G156" t="s">
         <v>6</v>
       </c>
       <c r="H156" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="I156" t="s">
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M156" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -5135,10 +5141,10 @@
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M157" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -5146,19 +5152,19 @@
         <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="C158" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="D158" t="s">
         <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="F158" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G158" t="s">
         <v>6</v>
@@ -5167,10 +5173,10 @@
         <v>8</v>
       </c>
       <c r="L158" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M158" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -5181,10 +5187,10 @@
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M159" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -5192,19 +5198,19 @@
         <v>1</v>
       </c>
       <c r="B160" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C160" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D160" t="s">
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="F160" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="G160" t="s">
         <v>6</v>
@@ -5213,7 +5219,7 @@
         <v>8</v>
       </c>
       <c r="L160" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M160" t="s">
         <v>106</v>
@@ -5224,19 +5230,19 @@
         <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="C161" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="D161" t="s">
         <v>3</v>
       </c>
       <c r="E161" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="F161" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="G161" t="s">
         <v>6</v>
@@ -5245,10 +5251,10 @@
         <v>8</v>
       </c>
       <c r="L161" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M161" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -5259,10 +5265,10 @@
         <v>8</v>
       </c>
       <c r="L162" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M162" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -5270,19 +5276,19 @@
         <v>1</v>
       </c>
       <c r="B163" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D163" t="s">
         <v>3</v>
       </c>
       <c r="E163" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="F163" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G163" t="s">
         <v>6</v>
@@ -5291,10 +5297,10 @@
         <v>8</v>
       </c>
       <c r="L163" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M163" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -5305,10 +5311,10 @@
         <v>8</v>
       </c>
       <c r="L164" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M164" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -5316,19 +5322,19 @@
         <v>1</v>
       </c>
       <c r="B165" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="C165" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="D165" t="s">
         <v>3</v>
       </c>
       <c r="E165" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F165" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G165" t="s">
         <v>6</v>
@@ -5337,10 +5343,10 @@
         <v>8</v>
       </c>
       <c r="L165" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M165" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -5351,10 +5357,10 @@
         <v>8</v>
       </c>
       <c r="L166" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M166" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -5362,19 +5368,19 @@
         <v>1</v>
       </c>
       <c r="B167" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="C167" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="D167" t="s">
         <v>3</v>
       </c>
       <c r="E167" t="s">
-        <v>41</v>
+        <v>250</v>
       </c>
       <c r="F167" t="s">
-        <v>41</v>
+        <v>250</v>
       </c>
       <c r="G167" t="s">
         <v>6</v>
@@ -5383,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="L167" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M167" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -5394,10 +5400,10 @@
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="F168" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="G168" t="s">
         <v>6</v>
@@ -5406,10 +5412,10 @@
         <v>8</v>
       </c>
       <c r="L168" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M168" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -5420,10 +5426,10 @@
         <v>8</v>
       </c>
       <c r="L169" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="M169" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -5431,19 +5437,19 @@
         <v>1</v>
       </c>
       <c r="B170" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="C170" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="D170" t="s">
         <v>3</v>
       </c>
       <c r="E170" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F170" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G170" t="s">
         <v>6</v>
@@ -5452,10 +5458,10 @@
         <v>8</v>
       </c>
       <c r="L170" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="M170" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -5463,13 +5469,13 @@
         <v>3</v>
       </c>
       <c r="H171" t="s">
-        <v>323</v>
+        <v>65</v>
       </c>
       <c r="I171" t="s">
         <v>8</v>
       </c>
       <c r="L171" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M171" t="s">
         <v>43</v>
@@ -5480,10 +5486,10 @@
         <v>14</v>
       </c>
       <c r="L172" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M172" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -5491,10 +5497,10 @@
         <v>14</v>
       </c>
       <c r="L173" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -5505,7 +5511,7 @@
         <v>8</v>
       </c>
       <c r="L174" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M174" t="s">
         <v>43</v>
@@ -5516,19 +5522,19 @@
         <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C175" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D175" t="s">
         <v>3</v>
       </c>
       <c r="E175" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F175" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G175" t="s">
         <v>6</v>
@@ -5537,10 +5543,10 @@
         <v>8</v>
       </c>
       <c r="L175" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M175" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -5551,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="L176" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M176" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -5562,19 +5568,19 @@
         <v>1</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D177" t="s">
         <v>3</v>
       </c>
       <c r="E177" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F177" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G177" t="s">
         <v>6</v>
@@ -5583,10 +5589,10 @@
         <v>8</v>
       </c>
       <c r="L177" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M177" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -5594,10 +5600,10 @@
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F178" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G178" t="s">
         <v>6</v>
@@ -5606,10 +5612,10 @@
         <v>8</v>
       </c>
       <c r="L178" t="s">
+        <v>335</v>
+      </c>
+      <c r="M178" t="s">
         <v>332</v>
-      </c>
-      <c r="M178" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -5620,10 +5626,10 @@
         <v>8</v>
       </c>
       <c r="L179" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M179" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -5631,19 +5637,19 @@
         <v>1</v>
       </c>
       <c r="B180" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="C180" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="D180" t="s">
         <v>3</v>
       </c>
       <c r="E180" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="F180" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="G180" t="s">
         <v>6</v>
@@ -5652,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="L180" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M180" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -5666,10 +5672,10 @@
         <v>8</v>
       </c>
       <c r="L181" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M181" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -5677,19 +5683,19 @@
         <v>1</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
       <c r="D182" t="s">
         <v>3</v>
       </c>
       <c r="E182" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="F182" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="G182" t="s">
         <v>6</v>
@@ -5698,10 +5704,10 @@
         <v>8</v>
       </c>
       <c r="L182" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="M182" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -5709,19 +5715,19 @@
         <v>1</v>
       </c>
       <c r="B183" t="s">
-        <v>128</v>
+        <v>342</v>
       </c>
       <c r="C183" t="s">
-        <v>128</v>
+        <v>342</v>
       </c>
       <c r="D183" t="s">
         <v>3</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="F183" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="G183" t="s">
         <v>6</v>
@@ -5730,10 +5736,10 @@
         <v>8</v>
       </c>
       <c r="L183" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M183" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -5744,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="L184" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M184" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -5755,19 +5761,19 @@
         <v>1</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C185" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D185" t="s">
         <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="F185" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="G185" t="s">
         <v>6</v>
@@ -5776,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="L185" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M185" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -5790,10 +5796,10 @@
         <v>8</v>
       </c>
       <c r="L186" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M186" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -5801,19 +5807,19 @@
         <v>1</v>
       </c>
       <c r="B187" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C187" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="D187" t="s">
         <v>3</v>
       </c>
       <c r="E187" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="F187" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="G187" t="s">
         <v>6</v>
@@ -5822,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="L187" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M187" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -5833,19 +5839,19 @@
         <v>1</v>
       </c>
       <c r="B188" t="s">
-        <v>271</v>
+        <v>72</v>
       </c>
       <c r="C188" t="s">
-        <v>271</v>
+        <v>72</v>
       </c>
       <c r="D188" t="s">
         <v>3</v>
       </c>
       <c r="E188" t="s">
-        <v>30</v>
+        <v>350</v>
       </c>
       <c r="F188" t="s">
-        <v>30</v>
+        <v>350</v>
       </c>
       <c r="G188" t="s">
         <v>6</v>
@@ -5854,10 +5860,10 @@
         <v>8</v>
       </c>
       <c r="L188" t="s">
+        <v>351</v>
+      </c>
+      <c r="M188" t="s">
         <v>346</v>
-      </c>
-      <c r="M188" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -5868,10 +5874,10 @@
         <v>8</v>
       </c>
       <c r="L189" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M189" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -5879,19 +5885,19 @@
         <v>1</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C190" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D190" t="s">
         <v>3</v>
       </c>
       <c r="E190" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F190" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="G190" t="s">
         <v>6</v>
@@ -5900,10 +5906,10 @@
         <v>8</v>
       </c>
       <c r="L190" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="M190" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -5914,10 +5920,10 @@
         <v>8</v>
       </c>
       <c r="L191" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="M191" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -5925,19 +5931,19 @@
         <v>1</v>
       </c>
       <c r="B192" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="C192" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="D192" t="s">
         <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="F192" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="G192" t="s">
         <v>6</v>
@@ -5946,10 +5952,10 @@
         <v>8</v>
       </c>
       <c r="L192" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M192" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -5957,13 +5963,13 @@
         <v>3</v>
       </c>
       <c r="H193" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I193" t="s">
         <v>8</v>
       </c>
       <c r="L193" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="M193" t="s">
         <v>43</v>
@@ -5974,19 +5980,19 @@
         <v>1</v>
       </c>
       <c r="B194" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="C194" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="D194" t="s">
         <v>3</v>
       </c>
       <c r="E194" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F194" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G194" t="s">
         <v>6</v>
@@ -5995,10 +6001,10 @@
         <v>8</v>
       </c>
       <c r="L194" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M194" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -6006,19 +6012,19 @@
         <v>1</v>
       </c>
       <c r="B195" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="C195" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="D195" t="s">
         <v>3</v>
       </c>
       <c r="E195" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="F195" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="G195" t="s">
         <v>6</v>
@@ -6027,10 +6033,10 @@
         <v>8</v>
       </c>
       <c r="L195" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="M195" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -6041,10 +6047,10 @@
         <v>8</v>
       </c>
       <c r="L196" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M196" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -6052,19 +6058,19 @@
         <v>1</v>
       </c>
       <c r="B197" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C197" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D197" t="s">
         <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="F197" t="s">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="G197" t="s">
         <v>6</v>
@@ -6073,10 +6079,10 @@
         <v>8</v>
       </c>
       <c r="L197" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M197" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -6087,10 +6093,10 @@
         <v>8</v>
       </c>
       <c r="L198" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M198" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -6098,19 +6104,19 @@
         <v>1</v>
       </c>
       <c r="B199" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="C199" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="D199" t="s">
         <v>3</v>
       </c>
       <c r="E199" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="F199" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="G199" t="s">
         <v>6</v>
@@ -6119,10 +6125,10 @@
         <v>8</v>
       </c>
       <c r="L199" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="M199" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -6133,10 +6139,10 @@
         <v>8</v>
       </c>
       <c r="L200" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M200" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -6144,19 +6150,19 @@
         <v>1</v>
       </c>
       <c r="B201" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="C201" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="D201" t="s">
         <v>3</v>
       </c>
       <c r="E201" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F201" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G201" t="s">
         <v>6</v>
@@ -6165,10 +6171,10 @@
         <v>8</v>
       </c>
       <c r="L201" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="M201" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -6176,19 +6182,19 @@
         <v>1</v>
       </c>
       <c r="B202" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C202" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D202" t="s">
         <v>3</v>
       </c>
       <c r="E202" t="s">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="F202" t="s">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="G202" t="s">
         <v>6</v>
@@ -6197,10 +6203,10 @@
         <v>8</v>
       </c>
       <c r="L202" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M202" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -6211,10 +6217,10 @@
         <v>8</v>
       </c>
       <c r="L203" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M203" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -6222,19 +6228,19 @@
         <v>1</v>
       </c>
       <c r="B204" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="C204" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="D204" t="s">
         <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="F204" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G204" t="s">
         <v>6</v>
@@ -6243,24 +6249,27 @@
         <v>8</v>
       </c>
       <c r="L204" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="M204" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="205" spans="1:13">
       <c r="A205">
         <v>28</v>
       </c>
+      <c r="H205" t="s">
+        <v>373</v>
+      </c>
       <c r="I205" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="L205" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="M205" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -6268,10 +6277,10 @@
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>252</v>
+        <v>72</v>
       </c>
       <c r="F206" t="s">
-        <v>252</v>
+        <v>72</v>
       </c>
       <c r="G206" t="s">
         <v>6</v>
@@ -6280,10 +6289,10 @@
         <v>8</v>
       </c>
       <c r="L206" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="M206" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -6291,19 +6300,19 @@
         <v>1</v>
       </c>
       <c r="B207" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="C207" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="D207" t="s">
         <v>3</v>
       </c>
       <c r="E207" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="F207" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="G207" t="s">
         <v>6</v>
@@ -6312,10 +6321,10 @@
         <v>8</v>
       </c>
       <c r="L207" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="M207" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -6326,10 +6335,10 @@
         <v>8</v>
       </c>
       <c r="L208" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="M208" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -6337,19 +6346,19 @@
         <v>1</v>
       </c>
       <c r="B209" t="s">
-        <v>30</v>
+        <v>291</v>
       </c>
       <c r="C209" t="s">
-        <v>30</v>
+        <v>291</v>
       </c>
       <c r="D209" t="s">
         <v>3</v>
       </c>
       <c r="E209" t="s">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="F209" t="s">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="G209" t="s">
         <v>6</v>
@@ -6358,7 +6367,7 @@
         <v>8</v>
       </c>
       <c r="L209" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M209" t="s">
         <v>29</v>
@@ -6372,10 +6381,10 @@
         <v>8</v>
       </c>
       <c r="L210" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M210" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -6383,25 +6392,25 @@
         <v>1</v>
       </c>
       <c r="B211" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="C211" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="D211" t="s">
         <v>3</v>
       </c>
       <c r="H211" t="s">
-        <v>323</v>
+        <v>384</v>
       </c>
       <c r="I211" t="s">
         <v>8</v>
       </c>
       <c r="L211" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="M211" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -6409,19 +6418,19 @@
         <v>1</v>
       </c>
       <c r="B212" t="s">
-        <v>69</v>
+        <v>207</v>
       </c>
       <c r="C212" t="s">
-        <v>69</v>
+        <v>207</v>
       </c>
       <c r="D212" t="s">
         <v>3</v>
       </c>
       <c r="E212" t="s">
-        <v>375</v>
+        <v>206</v>
       </c>
       <c r="F212" t="s">
-        <v>375</v>
+        <v>206</v>
       </c>
       <c r="G212" t="s">
         <v>6</v>
@@ -6430,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="L212" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M212" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -6444,10 +6453,10 @@
         <v>8</v>
       </c>
       <c r="L213" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="M213" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -6455,19 +6464,19 @@
         <v>1</v>
       </c>
       <c r="B214" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="D214" t="s">
         <v>3</v>
       </c>
       <c r="E214" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="F214" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="G214" t="s">
         <v>6</v>
@@ -6476,10 +6485,10 @@
         <v>8</v>
       </c>
       <c r="L214" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="M214" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -6490,10 +6499,10 @@
         <v>8</v>
       </c>
       <c r="L215" t="s">
+        <v>389</v>
+      </c>
+      <c r="M215" t="s">
         <v>383</v>
-      </c>
-      <c r="M215" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -6501,10 +6510,10 @@
         <v>1</v>
       </c>
       <c r="E216" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F216" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G216" t="s">
         <v>6</v>
@@ -6513,10 +6522,10 @@
         <v>8</v>
       </c>
       <c r="L216" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="M216" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -6527,10 +6536,10 @@
         <v>8</v>
       </c>
       <c r="L217" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M217" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -6538,25 +6547,25 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="F218" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="G218" t="s">
         <v>6</v>
       </c>
       <c r="H218" t="s">
-        <v>388</v>
+        <v>232</v>
       </c>
       <c r="I218" t="s">
         <v>8</v>
       </c>
       <c r="L218" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="M218" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -6564,19 +6573,19 @@
         <v>1</v>
       </c>
       <c r="B219" t="s">
-        <v>391</v>
+        <v>69</v>
       </c>
       <c r="C219" t="s">
-        <v>391</v>
+        <v>69</v>
       </c>
       <c r="D219" t="s">
         <v>3</v>
       </c>
       <c r="E219" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F219" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G219" t="s">
         <v>6</v>
@@ -6585,10 +6594,10 @@
         <v>8</v>
       </c>
       <c r="L219" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M219" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -6599,10 +6608,10 @@
         <v>8</v>
       </c>
       <c r="L220" t="s">
+        <v>397</v>
+      </c>
+      <c r="M220" t="s">
         <v>393</v>
-      </c>
-      <c r="M220" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -6610,19 +6619,19 @@
         <v>1</v>
       </c>
       <c r="B221" t="s">
-        <v>100</v>
+        <v>398</v>
       </c>
       <c r="C221" t="s">
-        <v>100</v>
+        <v>398</v>
       </c>
       <c r="D221" t="s">
         <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>366</v>
+        <v>282</v>
       </c>
       <c r="F221" t="s">
-        <v>366</v>
+        <v>282</v>
       </c>
       <c r="G221" t="s">
         <v>6</v>
@@ -6631,10 +6640,10 @@
         <v>8</v>
       </c>
       <c r="L221" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="M221" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -6645,10 +6654,10 @@
         <v>8</v>
       </c>
       <c r="L222" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M222" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -6656,25 +6665,25 @@
         <v>1</v>
       </c>
       <c r="B223" t="s">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="C223" t="s">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="D223" t="s">
         <v>3</v>
       </c>
       <c r="H223" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="I223" t="s">
         <v>8</v>
       </c>
       <c r="L223" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M223" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -6685,10 +6694,10 @@
         <v>8</v>
       </c>
       <c r="L224" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M224" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -6696,19 +6705,19 @@
         <v>1</v>
       </c>
       <c r="B225" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C225" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="D225" t="s">
         <v>3</v>
       </c>
       <c r="E225" t="s">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="F225" t="s">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="G225" t="s">
         <v>6</v>
@@ -6717,10 +6726,10 @@
         <v>8</v>
       </c>
       <c r="L225" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M225" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -6728,19 +6737,19 @@
         <v>1</v>
       </c>
       <c r="B226" t="s">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="C226" t="s">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D226" t="s">
         <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G226" t="s">
         <v>6</v>
@@ -6749,10 +6758,10 @@
         <v>8</v>
       </c>
       <c r="L226" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M226" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -6763,10 +6772,10 @@
         <v>8</v>
       </c>
       <c r="L227" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="M227" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -6774,10 +6783,10 @@
         <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="F228" t="s">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="G228" t="s">
         <v>6</v>
@@ -6786,10 +6795,10 @@
         <v>8</v>
       </c>
       <c r="L228" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="M228" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -6800,10 +6809,10 @@
         <v>8</v>
       </c>
       <c r="L229" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="M229" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -6811,25 +6820,25 @@
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="F230" t="s">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="G230" t="s">
         <v>6</v>
       </c>
       <c r="H230" t="s">
-        <v>406</v>
+        <v>210</v>
       </c>
       <c r="I230" t="s">
         <v>8</v>
       </c>
       <c r="L230" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M230" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -6837,19 +6846,19 @@
         <v>1</v>
       </c>
       <c r="B231" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="C231" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="D231" t="s">
         <v>3</v>
       </c>
       <c r="E231" t="s">
-        <v>202</v>
+        <v>321</v>
       </c>
       <c r="F231" t="s">
-        <v>202</v>
+        <v>321</v>
       </c>
       <c r="G231" t="s">
         <v>6</v>
@@ -6858,10 +6867,10 @@
         <v>8</v>
       </c>
       <c r="L231" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M231" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -6872,10 +6881,10 @@
         <v>8</v>
       </c>
       <c r="L232" t="s">
+        <v>413</v>
+      </c>
+      <c r="M232" t="s">
         <v>409</v>
-      </c>
-      <c r="M232" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -6883,19 +6892,19 @@
         <v>1</v>
       </c>
       <c r="B233" t="s">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="C233" t="s">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="D233" t="s">
         <v>3</v>
       </c>
       <c r="E233" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F233" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G233" t="s">
         <v>6</v>
@@ -6904,10 +6913,10 @@
         <v>8</v>
       </c>
       <c r="L233" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M233" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -6918,10 +6927,10 @@
         <v>8</v>
       </c>
       <c r="L234" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M234" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -6929,19 +6938,19 @@
         <v>1</v>
       </c>
       <c r="B235" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="C235" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="D235" t="s">
         <v>3</v>
       </c>
       <c r="E235" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="F235" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="G235" t="s">
         <v>6</v>
@@ -6950,10 +6959,10 @@
         <v>8</v>
       </c>
       <c r="L235" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M235" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -6961,25 +6970,25 @@
         <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="C236" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="D236" t="s">
         <v>3</v>
       </c>
       <c r="H236" t="s">
-        <v>228</v>
+        <v>119</v>
       </c>
       <c r="I236" t="s">
         <v>8</v>
       </c>
       <c r="L236" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="M236" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -6990,10 +6999,10 @@
         <v>8</v>
       </c>
       <c r="L237" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="M237" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -7001,19 +7010,19 @@
         <v>1</v>
       </c>
       <c r="B238" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C238" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D238" t="s">
         <v>3</v>
       </c>
       <c r="E238" t="s">
-        <v>271</v>
+        <v>69</v>
       </c>
       <c r="F238" t="s">
-        <v>271</v>
+        <v>69</v>
       </c>
       <c r="G238" t="s">
         <v>6</v>
@@ -7022,10 +7031,10 @@
         <v>8</v>
       </c>
       <c r="L238" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M238" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -7036,10 +7045,10 @@
         <v>8</v>
       </c>
       <c r="L239" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M239" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -7050,10 +7059,10 @@
         <v>8</v>
       </c>
       <c r="L240" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M240" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -7064,10 +7073,10 @@
         <v>8</v>
       </c>
       <c r="L241" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M241" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -7084,10 +7093,10 @@
         <v>3</v>
       </c>
       <c r="E242" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F242" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G242" t="s">
         <v>6</v>
@@ -7096,10 +7105,10 @@
         <v>8</v>
       </c>
       <c r="L242" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M242" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -7107,10 +7116,10 @@
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="F243" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="G243" t="s">
         <v>6</v>
@@ -7119,10 +7128,10 @@
         <v>8</v>
       </c>
       <c r="L243" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="M243" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -7133,10 +7142,10 @@
         <v>8</v>
       </c>
       <c r="L244" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M244" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -7144,19 +7153,19 @@
         <v>1</v>
       </c>
       <c r="B245" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="C245" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="D245" t="s">
         <v>3</v>
       </c>
       <c r="E245" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="F245" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="G245" t="s">
         <v>6</v>
@@ -7165,10 +7174,10 @@
         <v>8</v>
       </c>
       <c r="L245" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="M245" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -7179,10 +7188,10 @@
         <v>8</v>
       </c>
       <c r="L246" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="M246" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -7190,19 +7199,19 @@
         <v>1</v>
       </c>
       <c r="B247" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C247" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="D247" t="s">
         <v>3</v>
       </c>
       <c r="E247" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G247" t="s">
         <v>6</v>
@@ -7211,10 +7220,10 @@
         <v>8</v>
       </c>
       <c r="L247" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M247" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -7225,10 +7234,10 @@
         <v>8</v>
       </c>
       <c r="L248" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M248" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -7236,10 +7245,10 @@
         <v>1</v>
       </c>
       <c r="B249" t="s">
-        <v>103</v>
+        <v>321</v>
       </c>
       <c r="C249" t="s">
-        <v>103</v>
+        <v>321</v>
       </c>
       <c r="D249" t="s">
         <v>3</v>
@@ -7257,10 +7266,10 @@
         <v>8</v>
       </c>
       <c r="L249" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M249" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -7268,19 +7277,19 @@
         <v>1</v>
       </c>
       <c r="B250" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="C250" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="D250" t="s">
         <v>3</v>
       </c>
       <c r="E250" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="F250" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="G250" t="s">
         <v>6</v>
@@ -7289,10 +7298,10 @@
         <v>8</v>
       </c>
       <c r="L250" t="s">
+        <v>436</v>
+      </c>
+      <c r="M250" t="s">
         <v>432</v>
-      </c>
-      <c r="M250" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="251" spans="1:13">
@@ -7303,10 +7312,10 @@
         <v>8</v>
       </c>
       <c r="L251" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="M251" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="252" spans="1:13">
@@ -7314,19 +7323,19 @@
         <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C252" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D252" t="s">
         <v>3</v>
       </c>
       <c r="E252" t="s">
-        <v>166</v>
+        <v>251</v>
       </c>
       <c r="F252" t="s">
-        <v>166</v>
+        <v>251</v>
       </c>
       <c r="G252" t="s">
         <v>6</v>
@@ -7335,10 +7344,10 @@
         <v>8</v>
       </c>
       <c r="L252" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M252" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="253" spans="1:13">
@@ -7349,10 +7358,10 @@
         <v>8</v>
       </c>
       <c r="L253" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M253" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -7360,19 +7369,19 @@
         <v>1</v>
       </c>
       <c r="B254" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C254" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="D254" t="s">
         <v>3</v>
       </c>
       <c r="E254" t="s">
-        <v>200</v>
+        <v>309</v>
       </c>
       <c r="F254" t="s">
-        <v>200</v>
+        <v>309</v>
       </c>
       <c r="G254" t="s">
         <v>6</v>
@@ -7381,10 +7390,10 @@
         <v>8</v>
       </c>
       <c r="L254" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M254" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="255" spans="1:13">
@@ -7392,25 +7401,25 @@
         <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>439</v>
+        <v>62</v>
       </c>
       <c r="F255" t="s">
-        <v>439</v>
+        <v>62</v>
       </c>
       <c r="G255" t="s">
         <v>6</v>
       </c>
       <c r="H255" t="s">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="I255" t="s">
         <v>8</v>
       </c>
       <c r="L255" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M255" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="256" spans="1:13">
@@ -7421,10 +7430,10 @@
         <v>8</v>
       </c>
       <c r="L256" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M256" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="257" spans="1:13">
@@ -7432,19 +7441,19 @@
         <v>1</v>
       </c>
       <c r="B257" t="s">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="C257" t="s">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="D257" t="s">
         <v>3</v>
       </c>
       <c r="L257" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M257" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="258" spans="1:13">
@@ -7452,10 +7461,10 @@
         <v>14</v>
       </c>
       <c r="L258" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M258" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="259" spans="1:13">
@@ -7466,10 +7475,10 @@
         <v>8</v>
       </c>
       <c r="L259" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M259" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="260" spans="1:13">
@@ -7477,19 +7486,19 @@
         <v>1</v>
       </c>
       <c r="B260" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="C260" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="D260" t="s">
         <v>3</v>
       </c>
       <c r="E260" t="s">
-        <v>300</v>
+        <v>54</v>
       </c>
       <c r="F260" t="s">
-        <v>300</v>
+        <v>54</v>
       </c>
       <c r="G260" t="s">
         <v>6</v>
@@ -7498,10 +7507,10 @@
         <v>8</v>
       </c>
       <c r="L260" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M260" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="261" spans="1:13">
@@ -7509,25 +7518,25 @@
         <v>1</v>
       </c>
       <c r="B261" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C261" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D261" t="s">
         <v>3</v>
       </c>
       <c r="H261" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="I261" t="s">
         <v>8</v>
       </c>
       <c r="L261" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M261" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="262" spans="1:13">
@@ -7538,10 +7547,10 @@
         <v>8</v>
       </c>
       <c r="L262" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="M262" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="263" spans="1:13">
@@ -7549,19 +7558,19 @@
         <v>1</v>
       </c>
       <c r="B263" t="s">
-        <v>46</v>
+        <v>321</v>
       </c>
       <c r="C263" t="s">
-        <v>46</v>
+        <v>321</v>
       </c>
       <c r="D263" t="s">
         <v>3</v>
       </c>
       <c r="E263" t="s">
-        <v>366</v>
+        <v>218</v>
       </c>
       <c r="F263" t="s">
-        <v>366</v>
+        <v>218</v>
       </c>
       <c r="G263" t="s">
         <v>6</v>
@@ -7570,10 +7579,10 @@
         <v>8</v>
       </c>
       <c r="L263" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M263" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="264" spans="1:13">
@@ -7584,10 +7593,10 @@
         <v>8</v>
       </c>
       <c r="L264" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M264" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="265" spans="1:13">
@@ -7595,25 +7604,25 @@
         <v>1</v>
       </c>
       <c r="E265" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F265" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G265" t="s">
         <v>6</v>
       </c>
       <c r="H265" t="s">
-        <v>454</v>
+        <v>171</v>
       </c>
       <c r="I265" t="s">
         <v>8</v>
       </c>
       <c r="L265" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M265" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="266" spans="1:13">
@@ -7624,10 +7633,10 @@
         <v>8</v>
       </c>
       <c r="L266" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M266" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="267" spans="1:13">
@@ -7635,19 +7644,19 @@
         <v>1</v>
       </c>
       <c r="B267" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="C267" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="D267" t="s">
         <v>3</v>
       </c>
       <c r="E267" t="s">
-        <v>280</v>
+        <v>109</v>
       </c>
       <c r="F267" t="s">
-        <v>280</v>
+        <v>109</v>
       </c>
       <c r="G267" t="s">
         <v>6</v>
@@ -7656,10 +7665,10 @@
         <v>8</v>
       </c>
       <c r="L267" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M267" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="268" spans="1:13">
@@ -7667,10 +7676,10 @@
         <v>1</v>
       </c>
       <c r="E268" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="F268" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="G268" t="s">
         <v>6</v>
@@ -7679,10 +7688,10 @@
         <v>8</v>
       </c>
       <c r="L268" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M268" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="269" spans="1:13">
@@ -7693,10 +7702,10 @@
         <v>8</v>
       </c>
       <c r="L269" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M269" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="270" spans="1:13">
@@ -7704,19 +7713,19 @@
         <v>1</v>
       </c>
       <c r="B270" t="s">
-        <v>462</v>
+        <v>207</v>
       </c>
       <c r="C270" t="s">
-        <v>462</v>
+        <v>207</v>
       </c>
       <c r="D270" t="s">
         <v>3</v>
       </c>
       <c r="E270" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F270" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="G270" t="s">
         <v>6</v>
@@ -7725,10 +7734,10 @@
         <v>8</v>
       </c>
       <c r="L270" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M270" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="271" spans="1:13">
@@ -7736,13 +7745,13 @@
         <v>3</v>
       </c>
       <c r="H271" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I271" t="s">
         <v>8</v>
       </c>
       <c r="L271" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M271" t="s">
         <v>43</v>
@@ -7753,19 +7762,19 @@
         <v>1</v>
       </c>
       <c r="B272" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="C272" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="D272" t="s">
         <v>3</v>
       </c>
       <c r="E272" t="s">
-        <v>46</v>
+        <v>238</v>
       </c>
       <c r="F272" t="s">
-        <v>46</v>
+        <v>238</v>
       </c>
       <c r="G272" t="s">
         <v>6</v>
@@ -7774,10 +7783,10 @@
         <v>8</v>
       </c>
       <c r="L272" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M272" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="273" spans="1:13">
@@ -7788,10 +7797,10 @@
         <v>8</v>
       </c>
       <c r="L273" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M273" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="274" spans="1:13">
@@ -7799,19 +7808,19 @@
         <v>1</v>
       </c>
       <c r="B274" t="s">
-        <v>462</v>
+        <v>90</v>
       </c>
       <c r="C274" t="s">
-        <v>462</v>
+        <v>90</v>
       </c>
       <c r="D274" t="s">
         <v>3</v>
       </c>
       <c r="E274" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="F274" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="G274" t="s">
         <v>6</v>
@@ -7820,7 +7829,7 @@
         <v>8</v>
       </c>
       <c r="L274" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M274" t="s">
         <v>43</v>
@@ -7831,19 +7840,19 @@
         <v>1</v>
       </c>
       <c r="B275" t="s">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="C275" t="s">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="D275" t="s">
         <v>3</v>
       </c>
       <c r="E275" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="F275" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="G275" t="s">
         <v>6</v>
@@ -7852,10 +7861,10 @@
         <v>8</v>
       </c>
       <c r="L275" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M275" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="276" spans="1:13">
@@ -7866,10 +7875,10 @@
         <v>8</v>
       </c>
       <c r="L276" t="s">
+        <v>472</v>
+      </c>
+      <c r="M276" t="s">
         <v>471</v>
-      </c>
-      <c r="M276" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="277" spans="1:13">
@@ -7877,19 +7886,19 @@
         <v>1</v>
       </c>
       <c r="B277" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C277" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D277" t="s">
         <v>3</v>
       </c>
       <c r="E277" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F277" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G277" t="s">
         <v>6</v>
@@ -7898,10 +7907,10 @@
         <v>8</v>
       </c>
       <c r="L277" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M277" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="278" spans="1:13">
@@ -7912,10 +7921,10 @@
         <v>8</v>
       </c>
       <c r="L278" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M278" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="279" spans="1:13">
@@ -7923,19 +7932,19 @@
         <v>1</v>
       </c>
       <c r="B279" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C279" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D279" t="s">
         <v>3</v>
       </c>
       <c r="E279" t="s">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="F279" t="s">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="G279" t="s">
         <v>6</v>
@@ -7944,10 +7953,10 @@
         <v>8</v>
       </c>
       <c r="L279" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M279" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="280" spans="1:13">
@@ -7955,16 +7964,16 @@
         <v>1</v>
       </c>
       <c r="E280" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="F280" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="G280" t="s">
         <v>6</v>
       </c>
       <c r="H280" t="s">
-        <v>475</v>
+        <v>91</v>
       </c>
       <c r="I280" t="s">
         <v>8</v>
@@ -7973,7 +7982,7 @@
         <v>476</v>
       </c>
       <c r="M280" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="281" spans="1:13">
@@ -7995,19 +8004,19 @@
         <v>1</v>
       </c>
       <c r="B282" t="s">
-        <v>439</v>
+        <v>62</v>
       </c>
       <c r="C282" t="s">
-        <v>439</v>
+        <v>62</v>
       </c>
       <c r="D282" t="s">
         <v>3</v>
       </c>
       <c r="E282" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F282" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="G282" t="s">
         <v>6</v>
@@ -8041,19 +8050,19 @@
         <v>1</v>
       </c>
       <c r="B284" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C284" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D284" t="s">
         <v>3</v>
       </c>
       <c r="E284" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F284" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G284" t="s">
         <v>6</v>
@@ -8073,19 +8082,19 @@
         <v>1</v>
       </c>
       <c r="B285" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="C285" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="D285" t="s">
         <v>3</v>
       </c>
       <c r="E285" t="s">
-        <v>157</v>
+        <v>398</v>
       </c>
       <c r="F285" t="s">
-        <v>157</v>
+        <v>398</v>
       </c>
       <c r="G285" t="s">
         <v>6</v>
@@ -8119,19 +8128,19 @@
         <v>1</v>
       </c>
       <c r="B287" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
       <c r="C287" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
       <c r="D287" t="s">
         <v>3</v>
       </c>
       <c r="E287" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="F287" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="G287" t="s">
         <v>6</v>
@@ -8165,19 +8174,19 @@
         <v>1</v>
       </c>
       <c r="B289" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="C289" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="D289" t="s">
         <v>3</v>
       </c>
       <c r="E289" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F289" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="G289" t="s">
         <v>6</v>
@@ -8197,16 +8206,16 @@
         <v>3</v>
       </c>
       <c r="H290" t="s">
-        <v>191</v>
+        <v>489</v>
       </c>
       <c r="I290" t="s">
         <v>8</v>
       </c>
       <c r="L290" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M290" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="291" spans="1:13">
@@ -8214,19 +8223,19 @@
         <v>1</v>
       </c>
       <c r="B291" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C291" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D291" t="s">
         <v>3</v>
       </c>
       <c r="E291" t="s">
-        <v>375</v>
+        <v>118</v>
       </c>
       <c r="F291" t="s">
-        <v>375</v>
+        <v>118</v>
       </c>
       <c r="G291" t="s">
         <v>6</v>
@@ -8235,7 +8244,7 @@
         <v>8</v>
       </c>
       <c r="L291" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M291" t="s">
         <v>487</v>
@@ -8246,19 +8255,19 @@
         <v>1</v>
       </c>
       <c r="B292" t="s">
-        <v>462</v>
+        <v>58</v>
       </c>
       <c r="C292" t="s">
-        <v>462</v>
+        <v>58</v>
       </c>
       <c r="D292" t="s">
         <v>3</v>
       </c>
       <c r="E292" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="F292" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="G292" t="s">
         <v>6</v>
@@ -8267,10 +8276,10 @@
         <v>8</v>
       </c>
       <c r="L292" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M292" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="293" spans="1:13">
@@ -8281,7 +8290,7 @@
         <v>8</v>
       </c>
       <c r="L293" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M293" t="s">
         <v>43</v>
@@ -8292,19 +8301,19 @@
         <v>1</v>
       </c>
       <c r="B294" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="C294" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="D294" t="s">
         <v>3</v>
       </c>
       <c r="E294" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="F294" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="G294" t="s">
         <v>6</v>
@@ -8313,10 +8322,10 @@
         <v>8</v>
       </c>
       <c r="L294" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M294" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -8327,10 +8336,10 @@
         <v>8</v>
       </c>
       <c r="L295" t="s">
+        <v>497</v>
+      </c>
+      <c r="M295" t="s">
         <v>496</v>
-      </c>
-      <c r="M295" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="296" spans="1:13">
@@ -8338,19 +8347,19 @@
         <v>1</v>
       </c>
       <c r="B296" t="s">
-        <v>73</v>
+        <v>282</v>
       </c>
       <c r="C296" t="s">
-        <v>73</v>
+        <v>282</v>
       </c>
       <c r="D296" t="s">
         <v>3</v>
       </c>
       <c r="E296" t="s">
-        <v>265</v>
+        <v>62</v>
       </c>
       <c r="F296" t="s">
-        <v>265</v>
+        <v>62</v>
       </c>
       <c r="G296" t="s">
         <v>6</v>
@@ -8359,10 +8368,10 @@
         <v>8</v>
       </c>
       <c r="L296" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M296" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="297" spans="1:13">
@@ -8373,10 +8382,10 @@
         <v>8</v>
       </c>
       <c r="L297" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M297" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="298" spans="1:13">
@@ -8384,10 +8393,10 @@
         <v>1</v>
       </c>
       <c r="B298" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C298" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D298" t="s">
         <v>3</v>
@@ -8396,10 +8405,10 @@
         <v>8</v>
       </c>
       <c r="L298" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M298" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="299" spans="1:13">
@@ -8407,19 +8416,19 @@
         <v>1</v>
       </c>
       <c r="B299" t="s">
-        <v>41</v>
+        <v>309</v>
       </c>
       <c r="C299" t="s">
-        <v>41</v>
+        <v>309</v>
       </c>
       <c r="D299" t="s">
         <v>3</v>
       </c>
       <c r="E299" t="s">
-        <v>62</v>
+        <v>230</v>
       </c>
       <c r="F299" t="s">
-        <v>62</v>
+        <v>230</v>
       </c>
       <c r="G299" t="s">
         <v>6</v>
@@ -8428,10 +8437,10 @@
         <v>8</v>
       </c>
       <c r="L299" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M299" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="300" spans="1:13">
@@ -8442,10 +8451,10 @@
         <v>8</v>
       </c>
       <c r="L300" t="s">
+        <v>504</v>
+      </c>
+      <c r="M300" t="s">
         <v>503</v>
-      </c>
-      <c r="M300" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="301" spans="1:13">
@@ -8453,19 +8462,19 @@
         <v>1</v>
       </c>
       <c r="B301" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="C301" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="D301" t="s">
         <v>3</v>
       </c>
       <c r="E301" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F301" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G301" t="s">
         <v>6</v>
@@ -8474,10 +8483,10 @@
         <v>8</v>
       </c>
       <c r="L301" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M301" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="302" spans="1:13">
@@ -8488,10 +8497,10 @@
         <v>8</v>
       </c>
       <c r="L302" t="s">
+        <v>507</v>
+      </c>
+      <c r="M302" t="s">
         <v>506</v>
-      </c>
-      <c r="M302" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="303" spans="1:13">
@@ -8502,10 +8511,10 @@
         <v>8</v>
       </c>
       <c r="L303" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M303" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="304" spans="1:13">
@@ -8513,19 +8522,19 @@
         <v>1</v>
       </c>
       <c r="B304" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C304" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D304" t="s">
         <v>3</v>
       </c>
       <c r="E304" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F304" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="G304" t="s">
         <v>6</v>
@@ -8534,7 +8543,7 @@
         <v>8</v>
       </c>
       <c r="L304" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M304" t="s">
         <v>43</v>
@@ -8545,10 +8554,10 @@
         <v>14</v>
       </c>
       <c r="L305" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M305" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="306" spans="1:13">
@@ -8559,7 +8568,7 @@
         <v>36</v>
       </c>
       <c r="L306" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M306" t="s">
         <v>38</v>
@@ -8570,19 +8579,19 @@
         <v>1</v>
       </c>
       <c r="B307" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C307" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D307" t="s">
         <v>3</v>
       </c>
       <c r="E307" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="F307" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="G307" t="s">
         <v>6</v>
@@ -8591,10 +8600,10 @@
         <v>8</v>
       </c>
       <c r="L307" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M307" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="308" spans="1:13">
@@ -8605,10 +8614,10 @@
         <v>8</v>
       </c>
       <c r="L308" t="s">
+        <v>514</v>
+      </c>
+      <c r="M308" t="s">
         <v>513</v>
-      </c>
-      <c r="M308" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="309" spans="1:13">
@@ -8616,19 +8625,19 @@
         <v>1</v>
       </c>
       <c r="B309" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C309" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D309" t="s">
         <v>3</v>
       </c>
       <c r="E309" t="s">
-        <v>391</v>
+        <v>64</v>
       </c>
       <c r="F309" t="s">
-        <v>391</v>
+        <v>64</v>
       </c>
       <c r="G309" t="s">
         <v>6</v>
@@ -8637,10 +8646,10 @@
         <v>8</v>
       </c>
       <c r="L309" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M309" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="310" spans="1:13">
@@ -8648,25 +8657,25 @@
         <v>1</v>
       </c>
       <c r="B310" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="C310" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="D310" t="s">
         <v>3</v>
       </c>
       <c r="H310" t="s">
-        <v>228</v>
+        <v>516</v>
       </c>
       <c r="I310" t="s">
         <v>8</v>
       </c>
       <c r="L310" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M310" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="311" spans="1:13">
@@ -8677,10 +8686,10 @@
         <v>8</v>
       </c>
       <c r="L311" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M311" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="312" spans="1:13">
@@ -8688,10 +8697,10 @@
         <v>14</v>
       </c>
       <c r="L312" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M312" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="313" spans="1:13">
@@ -8702,10 +8711,10 @@
         <v>8</v>
       </c>
       <c r="L313" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M313" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="314" spans="1:13">
@@ -8713,19 +8722,19 @@
         <v>1</v>
       </c>
       <c r="B314" t="s">
-        <v>265</v>
+        <v>398</v>
       </c>
       <c r="C314" t="s">
-        <v>265</v>
+        <v>398</v>
       </c>
       <c r="D314" t="s">
         <v>3</v>
       </c>
       <c r="E314" t="s">
-        <v>462</v>
+        <v>46</v>
       </c>
       <c r="F314" t="s">
-        <v>462</v>
+        <v>46</v>
       </c>
       <c r="G314" t="s">
         <v>6</v>
@@ -8734,10 +8743,10 @@
         <v>8</v>
       </c>
       <c r="L314" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M314" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="315" spans="1:13">
@@ -8748,10 +8757,10 @@
         <v>8</v>
       </c>
       <c r="L315" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M315" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="316" spans="1:13">
@@ -8759,19 +8768,19 @@
         <v>1</v>
       </c>
       <c r="B316" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="C316" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="D316" t="s">
         <v>3</v>
       </c>
       <c r="E316" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="F316" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="G316" t="s">
         <v>6</v>
@@ -8780,10 +8789,10 @@
         <v>8</v>
       </c>
       <c r="L316" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M316" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="317" spans="1:13">
@@ -8794,10 +8803,10 @@
         <v>8</v>
       </c>
       <c r="L317" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M317" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="318" spans="1:13">
@@ -8805,19 +8814,19 @@
         <v>1</v>
       </c>
       <c r="B318" t="s">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="C318" t="s">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="D318" t="s">
         <v>3</v>
       </c>
       <c r="E318" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="F318" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="G318" t="s">
         <v>6</v>
@@ -8826,10 +8835,10 @@
         <v>8</v>
       </c>
       <c r="L318" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M318" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="319" spans="1:13">
@@ -8840,10 +8849,10 @@
         <v>8</v>
       </c>
       <c r="L319" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M319" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="320" spans="1:13">
@@ -8851,19 +8860,19 @@
         <v>1</v>
       </c>
       <c r="B320" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="C320" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D320" t="s">
         <v>3</v>
       </c>
       <c r="E320" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="F320" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="G320" t="s">
         <v>6</v>
@@ -8872,10 +8881,10 @@
         <v>8</v>
       </c>
       <c r="L320" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M320" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="321" spans="1:13">
@@ -8883,10 +8892,10 @@
         <v>14</v>
       </c>
       <c r="L321" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M321" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="322" spans="1:13">
@@ -8897,7 +8906,7 @@
         <v>36</v>
       </c>
       <c r="L322" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M322" t="s">
         <v>38</v>
@@ -8908,10 +8917,10 @@
         <v>1</v>
       </c>
       <c r="B323" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C323" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D323" t="s">
         <v>3</v>
@@ -8920,10 +8929,10 @@
         <v>8</v>
       </c>
       <c r="L323" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M323" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="324" spans="1:13">
@@ -8934,10 +8943,10 @@
         <v>8</v>
       </c>
       <c r="L324" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M324" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="325" spans="1:13">
@@ -8945,19 +8954,19 @@
         <v>1</v>
       </c>
       <c r="B325" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="C325" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="D325" t="s">
         <v>3</v>
       </c>
       <c r="E325" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F325" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G325" t="s">
         <v>6</v>
@@ -8966,10 +8975,10 @@
         <v>8</v>
       </c>
       <c r="L325" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M325" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="326" spans="1:13">
@@ -8977,10 +8986,10 @@
         <v>14</v>
       </c>
       <c r="L326" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M326" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="327" spans="1:13">
@@ -8991,7 +9000,7 @@
         <v>36</v>
       </c>
       <c r="L327" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M327" t="s">
         <v>38</v>
@@ -9002,10 +9011,10 @@
         <v>1</v>
       </c>
       <c r="E328" t="s">
-        <v>260</v>
+        <v>54</v>
       </c>
       <c r="F328" t="s">
-        <v>260</v>
+        <v>54</v>
       </c>
       <c r="G328" t="s">
         <v>6</v>
@@ -9014,10 +9023,10 @@
         <v>8</v>
       </c>
       <c r="L328" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M328" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="329" spans="1:13">
@@ -9025,19 +9034,19 @@
         <v>1</v>
       </c>
       <c r="B329" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C329" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D329" t="s">
         <v>3</v>
       </c>
       <c r="E329" t="s">
-        <v>157</v>
+        <v>398</v>
       </c>
       <c r="F329" t="s">
-        <v>157</v>
+        <v>398</v>
       </c>
       <c r="G329" t="s">
         <v>6</v>
@@ -9046,10 +9055,10 @@
         <v>8</v>
       </c>
       <c r="L329" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M329" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="330" spans="1:13">
@@ -9057,16 +9066,16 @@
         <v>3</v>
       </c>
       <c r="H330" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="I330" t="s">
         <v>8</v>
       </c>
       <c r="L330" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M330" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="331" spans="1:13">
@@ -9074,19 +9083,19 @@
         <v>1</v>
       </c>
       <c r="B331" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C331" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D331" t="s">
         <v>3</v>
       </c>
       <c r="E331" t="s">
-        <v>200</v>
+        <v>342</v>
       </c>
       <c r="F331" t="s">
-        <v>200</v>
+        <v>342</v>
       </c>
       <c r="G331" t="s">
         <v>6</v>
@@ -9095,10 +9104,10 @@
         <v>8</v>
       </c>
       <c r="L331" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M331" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="332" spans="1:13">
@@ -9109,10 +9118,10 @@
         <v>8</v>
       </c>
       <c r="L332" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M332" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="333" spans="1:13">
@@ -9123,10 +9132,10 @@
         <v>8</v>
       </c>
       <c r="L333" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M333" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="334" spans="1:13">
@@ -9134,19 +9143,19 @@
         <v>1</v>
       </c>
       <c r="B334" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C334" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D334" t="s">
         <v>3</v>
       </c>
       <c r="E334" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="F334" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="G334" t="s">
         <v>6</v>
@@ -9155,10 +9164,10 @@
         <v>8</v>
       </c>
       <c r="L334" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M334" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="335" spans="1:13">
@@ -9166,10 +9175,10 @@
         <v>1</v>
       </c>
       <c r="B335" t="s">
-        <v>24</v>
+        <v>218</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
+        <v>218</v>
       </c>
       <c r="D335" t="s">
         <v>3</v>
@@ -9178,10 +9187,10 @@
         <v>8</v>
       </c>
       <c r="L335" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M335" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="336" spans="1:13">
@@ -9192,10 +9201,10 @@
         <v>8</v>
       </c>
       <c r="L336" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M336" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="337" spans="1:13">
@@ -9203,19 +9212,19 @@
         <v>1</v>
       </c>
       <c r="B337" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="C337" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="D337" t="s">
         <v>3</v>
       </c>
       <c r="E337" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="F337" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G337" t="s">
         <v>6</v>
@@ -9224,10 +9233,10 @@
         <v>8</v>
       </c>
       <c r="L337" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M337" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="338" spans="1:13">
@@ -9238,10 +9247,10 @@
         <v>8</v>
       </c>
       <c r="L338" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M338" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="339" spans="1:13">
@@ -9252,10 +9261,10 @@
         <v>8</v>
       </c>
       <c r="L339" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M339" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="340" spans="1:13">
@@ -9263,10 +9272,10 @@
         <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="F340" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="G340" t="s">
         <v>6</v>
@@ -9275,10 +9284,10 @@
         <v>8</v>
       </c>
       <c r="L340" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M340" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="341" spans="1:13">
@@ -9286,19 +9295,19 @@
         <v>1</v>
       </c>
       <c r="B341" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C341" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="D341" t="s">
         <v>3</v>
       </c>
       <c r="E341" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="F341" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="G341" t="s">
         <v>6</v>
@@ -9307,10 +9316,10 @@
         <v>8</v>
       </c>
       <c r="L341" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M341" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="342" spans="1:13">
@@ -9321,10 +9330,10 @@
         <v>8</v>
       </c>
       <c r="L342" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M342" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
